--- a/Data.xlsx
+++ b/Data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahasa\OneDrive\Desktop\Codes\Predicting-Rejsekort-Price-Increase\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3785" uniqueCount="3677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4252" uniqueCount="4120">
   <si>
     <t>Afgangsdato År - Måned - Dato</t>
   </si>
@@ -11075,6 +11075,1335 @@
   </si>
   <si>
     <t>31-12-2022</t>
+  </si>
+  <si>
+    <t>13-01-2023</t>
+  </si>
+  <si>
+    <t>14-01-2023</t>
+  </si>
+  <si>
+    <t>15-01-2023</t>
+  </si>
+  <si>
+    <t>16-01-2023</t>
+  </si>
+  <si>
+    <t>17-01-2023</t>
+  </si>
+  <si>
+    <t>18-01-2023</t>
+  </si>
+  <si>
+    <t>19-01-2023</t>
+  </si>
+  <si>
+    <t>20-01-2023</t>
+  </si>
+  <si>
+    <t>21-01-2023</t>
+  </si>
+  <si>
+    <t>22-01-2023</t>
+  </si>
+  <si>
+    <t>23-01-2023</t>
+  </si>
+  <si>
+    <t>24-01-2023</t>
+  </si>
+  <si>
+    <t>25-01-2023</t>
+  </si>
+  <si>
+    <t>26-01-2023</t>
+  </si>
+  <si>
+    <t>27-01-2023</t>
+  </si>
+  <si>
+    <t>28-01-2023</t>
+  </si>
+  <si>
+    <t>29-01-2023</t>
+  </si>
+  <si>
+    <t>30-01-2023</t>
+  </si>
+  <si>
+    <t>31-01-2023</t>
+  </si>
+  <si>
+    <t>13-02-2023</t>
+  </si>
+  <si>
+    <t>14-02-2023</t>
+  </si>
+  <si>
+    <t>15-02-2023</t>
+  </si>
+  <si>
+    <t>16-02-2023</t>
+  </si>
+  <si>
+    <t>17-02-2023</t>
+  </si>
+  <si>
+    <t>18-02-2023</t>
+  </si>
+  <si>
+    <t>19-02-2023</t>
+  </si>
+  <si>
+    <t>20-02-2023</t>
+  </si>
+  <si>
+    <t>21-02-2023</t>
+  </si>
+  <si>
+    <t>22-02-2023</t>
+  </si>
+  <si>
+    <t>23-02-2023</t>
+  </si>
+  <si>
+    <t>24-02-2023</t>
+  </si>
+  <si>
+    <t>25-02-2023</t>
+  </si>
+  <si>
+    <t>26-02-2023</t>
+  </si>
+  <si>
+    <t>27-02-2023</t>
+  </si>
+  <si>
+    <t>28-02-2023</t>
+  </si>
+  <si>
+    <t>13-03-2023</t>
+  </si>
+  <si>
+    <t>14-03-2023</t>
+  </si>
+  <si>
+    <t>15-03-2023</t>
+  </si>
+  <si>
+    <t>16-03-2023</t>
+  </si>
+  <si>
+    <t>17-03-2023</t>
+  </si>
+  <si>
+    <t>18-03-2023</t>
+  </si>
+  <si>
+    <t>19-03-2023</t>
+  </si>
+  <si>
+    <t>20-03-2023</t>
+  </si>
+  <si>
+    <t>21-03-2023</t>
+  </si>
+  <si>
+    <t>22-03-2023</t>
+  </si>
+  <si>
+    <t>23-03-2023</t>
+  </si>
+  <si>
+    <t>24-03-2023</t>
+  </si>
+  <si>
+    <t>25-03-2023</t>
+  </si>
+  <si>
+    <t>26-03-2023</t>
+  </si>
+  <si>
+    <t>27-03-2023</t>
+  </si>
+  <si>
+    <t>28-03-2023</t>
+  </si>
+  <si>
+    <t>29-03-2023</t>
+  </si>
+  <si>
+    <t>30-03-2023</t>
+  </si>
+  <si>
+    <t>31-03-2023</t>
+  </si>
+  <si>
+    <t>13-04-2023</t>
+  </si>
+  <si>
+    <t>14-04-2023</t>
+  </si>
+  <si>
+    <t>15-04-2023</t>
+  </si>
+  <si>
+    <t>16-04-2023</t>
+  </si>
+  <si>
+    <t>17-04-2023</t>
+  </si>
+  <si>
+    <t>18-04-2023</t>
+  </si>
+  <si>
+    <t>19-04-2023</t>
+  </si>
+  <si>
+    <t>20-04-2023</t>
+  </si>
+  <si>
+    <t>21-04-2023</t>
+  </si>
+  <si>
+    <t>22-04-2023</t>
+  </si>
+  <si>
+    <t>23-04-2023</t>
+  </si>
+  <si>
+    <t>24-04-2023</t>
+  </si>
+  <si>
+    <t>25-04-2023</t>
+  </si>
+  <si>
+    <t>26-04-2023</t>
+  </si>
+  <si>
+    <t>27-04-2023</t>
+  </si>
+  <si>
+    <t>28-04-2023</t>
+  </si>
+  <si>
+    <t>29-04-2023</t>
+  </si>
+  <si>
+    <t>30-04-2023</t>
+  </si>
+  <si>
+    <t>13-05-2023</t>
+  </si>
+  <si>
+    <t>14-05-2023</t>
+  </si>
+  <si>
+    <t>15-05-2023</t>
+  </si>
+  <si>
+    <t>16-05-2023</t>
+  </si>
+  <si>
+    <t>17-05-2023</t>
+  </si>
+  <si>
+    <t>18-05-2023</t>
+  </si>
+  <si>
+    <t>19-05-2023</t>
+  </si>
+  <si>
+    <t>20-05-2023</t>
+  </si>
+  <si>
+    <t>21-05-2023</t>
+  </si>
+  <si>
+    <t>22-05-2023</t>
+  </si>
+  <si>
+    <t>23-05-2023</t>
+  </si>
+  <si>
+    <t>24-05-2023</t>
+  </si>
+  <si>
+    <t>25-05-2023</t>
+  </si>
+  <si>
+    <t>26-05-2023</t>
+  </si>
+  <si>
+    <t>27-05-2023</t>
+  </si>
+  <si>
+    <t>28-05-2023</t>
+  </si>
+  <si>
+    <t>29-05-2023</t>
+  </si>
+  <si>
+    <t>30-05-2023</t>
+  </si>
+  <si>
+    <t>31-05-2023</t>
+  </si>
+  <si>
+    <t>13-06-2023</t>
+  </si>
+  <si>
+    <t>14-06-2023</t>
+  </si>
+  <si>
+    <t>15-06-2023</t>
+  </si>
+  <si>
+    <t>16-06-2023</t>
+  </si>
+  <si>
+    <t>17-06-2023</t>
+  </si>
+  <si>
+    <t>18-06-2023</t>
+  </si>
+  <si>
+    <t>19-06-2023</t>
+  </si>
+  <si>
+    <t>20-06-2023</t>
+  </si>
+  <si>
+    <t>21-06-2023</t>
+  </si>
+  <si>
+    <t>22-06-2023</t>
+  </si>
+  <si>
+    <t>23-06-2023</t>
+  </si>
+  <si>
+    <t>24-06-2023</t>
+  </si>
+  <si>
+    <t>25-06-2023</t>
+  </si>
+  <si>
+    <t>26-06-2023</t>
+  </si>
+  <si>
+    <t>27-06-2023</t>
+  </si>
+  <si>
+    <t>28-06-2023</t>
+  </si>
+  <si>
+    <t>29-06-2023</t>
+  </si>
+  <si>
+    <t>30-06-2023</t>
+  </si>
+  <si>
+    <t>13-07-2023</t>
+  </si>
+  <si>
+    <t>14-07-2023</t>
+  </si>
+  <si>
+    <t>15-07-2023</t>
+  </si>
+  <si>
+    <t>16-07-2023</t>
+  </si>
+  <si>
+    <t>17-07-2023</t>
+  </si>
+  <si>
+    <t>18-07-2023</t>
+  </si>
+  <si>
+    <t>19-07-2023</t>
+  </si>
+  <si>
+    <t>20-07-2023</t>
+  </si>
+  <si>
+    <t>21-07-2023</t>
+  </si>
+  <si>
+    <t>22-07-2023</t>
+  </si>
+  <si>
+    <t>23-07-2023</t>
+  </si>
+  <si>
+    <t>24-07-2023</t>
+  </si>
+  <si>
+    <t>25-07-2023</t>
+  </si>
+  <si>
+    <t>26-07-2023</t>
+  </si>
+  <si>
+    <t>27-07-2023</t>
+  </si>
+  <si>
+    <t>28-07-2023</t>
+  </si>
+  <si>
+    <t>29-07-2023</t>
+  </si>
+  <si>
+    <t>30-07-2023</t>
+  </si>
+  <si>
+    <t>31-07-2023</t>
+  </si>
+  <si>
+    <t>13-08-2023</t>
+  </si>
+  <si>
+    <t>14-08-2023</t>
+  </si>
+  <si>
+    <t>15-08-2023</t>
+  </si>
+  <si>
+    <t>16-08-2023</t>
+  </si>
+  <si>
+    <t>17-08-2023</t>
+  </si>
+  <si>
+    <t>18-08-2023</t>
+  </si>
+  <si>
+    <t>19-08-2023</t>
+  </si>
+  <si>
+    <t>20-08-2023</t>
+  </si>
+  <si>
+    <t>21-08-2023</t>
+  </si>
+  <si>
+    <t>22-08-2023</t>
+  </si>
+  <si>
+    <t>23-08-2023</t>
+  </si>
+  <si>
+    <t>24-08-2023</t>
+  </si>
+  <si>
+    <t>25-08-2023</t>
+  </si>
+  <si>
+    <t>26-08-2023</t>
+  </si>
+  <si>
+    <t>27-08-2023</t>
+  </si>
+  <si>
+    <t>28-08-2023</t>
+  </si>
+  <si>
+    <t>29-08-2023</t>
+  </si>
+  <si>
+    <t>30-08-2023</t>
+  </si>
+  <si>
+    <t>31-08-2023</t>
+  </si>
+  <si>
+    <t>13-09-2023</t>
+  </si>
+  <si>
+    <t>14-09-2023</t>
+  </si>
+  <si>
+    <t>15-09-2023</t>
+  </si>
+  <si>
+    <t>16-09-2023</t>
+  </si>
+  <si>
+    <t>17-09-2023</t>
+  </si>
+  <si>
+    <t>18-09-2023</t>
+  </si>
+  <si>
+    <t>19-09-2023</t>
+  </si>
+  <si>
+    <t>20-09-2023</t>
+  </si>
+  <si>
+    <t>21-09-2023</t>
+  </si>
+  <si>
+    <t>22-09-2023</t>
+  </si>
+  <si>
+    <t>23-09-2023</t>
+  </si>
+  <si>
+    <t>24-09-2023</t>
+  </si>
+  <si>
+    <t>25-09-2023</t>
+  </si>
+  <si>
+    <t>26-09-2023</t>
+  </si>
+  <si>
+    <t>27-09-2023</t>
+  </si>
+  <si>
+    <t>28-09-2023</t>
+  </si>
+  <si>
+    <t>29-09-2023</t>
+  </si>
+  <si>
+    <t>30-09-2023</t>
+  </si>
+  <si>
+    <t>13-10-2023</t>
+  </si>
+  <si>
+    <t>14-10-2023</t>
+  </si>
+  <si>
+    <t>15-10-2023</t>
+  </si>
+  <si>
+    <t>16-10-2023</t>
+  </si>
+  <si>
+    <t>17-10-2023</t>
+  </si>
+  <si>
+    <t>18-10-2023</t>
+  </si>
+  <si>
+    <t>19-10-2023</t>
+  </si>
+  <si>
+    <t>20-10-2023</t>
+  </si>
+  <si>
+    <t>21-10-2023</t>
+  </si>
+  <si>
+    <t>22-10-2023</t>
+  </si>
+  <si>
+    <t>23-10-2023</t>
+  </si>
+  <si>
+    <t>24-10-2023</t>
+  </si>
+  <si>
+    <t>25-10-2023</t>
+  </si>
+  <si>
+    <t>26-10-2023</t>
+  </si>
+  <si>
+    <t>27-10-2023</t>
+  </si>
+  <si>
+    <t>28-10-2023</t>
+  </si>
+  <si>
+    <t>29-10-2023</t>
+  </si>
+  <si>
+    <t>30-10-2023</t>
+  </si>
+  <si>
+    <t>31-10-2023</t>
+  </si>
+  <si>
+    <t>13-11-2023</t>
+  </si>
+  <si>
+    <t>14-11-2023</t>
+  </si>
+  <si>
+    <t>15-11-2023</t>
+  </si>
+  <si>
+    <t>16-11-2023</t>
+  </si>
+  <si>
+    <t>17-11-2023</t>
+  </si>
+  <si>
+    <t>18-11-2023</t>
+  </si>
+  <si>
+    <t>19-11-2023</t>
+  </si>
+  <si>
+    <t>20-11-2023</t>
+  </si>
+  <si>
+    <t>21-11-2023</t>
+  </si>
+  <si>
+    <t>22-11-2023</t>
+  </si>
+  <si>
+    <t>23-11-2023</t>
+  </si>
+  <si>
+    <t>24-11-2023</t>
+  </si>
+  <si>
+    <t>25-11-2023</t>
+  </si>
+  <si>
+    <t>26-11-2023</t>
+  </si>
+  <si>
+    <t>27-11-2023</t>
+  </si>
+  <si>
+    <t>28-11-2023</t>
+  </si>
+  <si>
+    <t>29-11-2023</t>
+  </si>
+  <si>
+    <t>30-11-2023</t>
+  </si>
+  <si>
+    <t>13-12-2023</t>
+  </si>
+  <si>
+    <t>14-12-2023</t>
+  </si>
+  <si>
+    <t>15-12-2023</t>
+  </si>
+  <si>
+    <t>16-12-2023</t>
+  </si>
+  <si>
+    <t>17-12-2023</t>
+  </si>
+  <si>
+    <t>18-12-2023</t>
+  </si>
+  <si>
+    <t>19-12-2023</t>
+  </si>
+  <si>
+    <t>20-12-2023</t>
+  </si>
+  <si>
+    <t>21-12-2023</t>
+  </si>
+  <si>
+    <t>22-12-2023</t>
+  </si>
+  <si>
+    <t>23-12-2023</t>
+  </si>
+  <si>
+    <t>24-12-2023</t>
+  </si>
+  <si>
+    <t>25-12-2023</t>
+  </si>
+  <si>
+    <t>26-12-2023</t>
+  </si>
+  <si>
+    <t>27-12-2023</t>
+  </si>
+  <si>
+    <t>28-12-2023</t>
+  </si>
+  <si>
+    <t>29-12-2023</t>
+  </si>
+  <si>
+    <t>30-12-2023</t>
+  </si>
+  <si>
+    <t>31-12-2023</t>
+  </si>
+  <si>
+    <t>13-01-2024</t>
+  </si>
+  <si>
+    <t>14-01-2024</t>
+  </si>
+  <si>
+    <t>15-01-2024</t>
+  </si>
+  <si>
+    <t>16-01-2024</t>
+  </si>
+  <si>
+    <t>17-01-2024</t>
+  </si>
+  <si>
+    <t>18-01-2024</t>
+  </si>
+  <si>
+    <t>19-01-2024</t>
+  </si>
+  <si>
+    <t>20-01-2024</t>
+  </si>
+  <si>
+    <t>21-01-2024</t>
+  </si>
+  <si>
+    <t>22-01-2024</t>
+  </si>
+  <si>
+    <t>23-01-2024</t>
+  </si>
+  <si>
+    <t>24-01-2024</t>
+  </si>
+  <si>
+    <t>25-01-2024</t>
+  </si>
+  <si>
+    <t>26-01-2024</t>
+  </si>
+  <si>
+    <t>27-01-2024</t>
+  </si>
+  <si>
+    <t>28-01-2024</t>
+  </si>
+  <si>
+    <t>29-01-2024</t>
+  </si>
+  <si>
+    <t>30-01-2024</t>
+  </si>
+  <si>
+    <t>31-01-2024</t>
+  </si>
+  <si>
+    <t>13-02-2024</t>
+  </si>
+  <si>
+    <t>14-02-2024</t>
+  </si>
+  <si>
+    <t>15-02-2024</t>
+  </si>
+  <si>
+    <t>16-02-2024</t>
+  </si>
+  <si>
+    <t>17-02-2024</t>
+  </si>
+  <si>
+    <t>18-02-2024</t>
+  </si>
+  <si>
+    <t>19-02-2024</t>
+  </si>
+  <si>
+    <t>20-02-2024</t>
+  </si>
+  <si>
+    <t>21-02-2024</t>
+  </si>
+  <si>
+    <t>22-02-2024</t>
+  </si>
+  <si>
+    <t>23-02-2024</t>
+  </si>
+  <si>
+    <t>24-02-2024</t>
+  </si>
+  <si>
+    <t>25-02-2024</t>
+  </si>
+  <si>
+    <t>26-02-2024</t>
+  </si>
+  <si>
+    <t>27-02-2024</t>
+  </si>
+  <si>
+    <t>28-02-2024</t>
+  </si>
+  <si>
+    <t>29-02-2024</t>
+  </si>
+  <si>
+    <t>13-03-2024</t>
+  </si>
+  <si>
+    <t>14-03-2024</t>
+  </si>
+  <si>
+    <t>15-03-2024</t>
+  </si>
+  <si>
+    <t>16-03-2024</t>
+  </si>
+  <si>
+    <t>17-03-2024</t>
+  </si>
+  <si>
+    <t>18-03-2024</t>
+  </si>
+  <si>
+    <t>19-03-2024</t>
+  </si>
+  <si>
+    <t>20-03-2024</t>
+  </si>
+  <si>
+    <t>21-03-2024</t>
+  </si>
+  <si>
+    <t>22-03-2024</t>
+  </si>
+  <si>
+    <t>23-03-2024</t>
+  </si>
+  <si>
+    <t>24-03-2024</t>
+  </si>
+  <si>
+    <t>25-03-2024</t>
+  </si>
+  <si>
+    <t>26-03-2024</t>
+  </si>
+  <si>
+    <t>27-03-2024</t>
+  </si>
+  <si>
+    <t>28-03-2024</t>
+  </si>
+  <si>
+    <t>29-03-2024</t>
+  </si>
+  <si>
+    <t>30-03-2024</t>
+  </si>
+  <si>
+    <t>31-03-2024</t>
+  </si>
+  <si>
+    <t>13-04-2024</t>
+  </si>
+  <si>
+    <t>14-04-2024</t>
+  </si>
+  <si>
+    <t>15-04-2024</t>
+  </si>
+  <si>
+    <t>16-04-2024</t>
+  </si>
+  <si>
+    <t>17-04-2024</t>
+  </si>
+  <si>
+    <t>18-04-2024</t>
+  </si>
+  <si>
+    <t>19-04-2024</t>
+  </si>
+  <si>
+    <t>20-04-2024</t>
+  </si>
+  <si>
+    <t>21-04-2024</t>
+  </si>
+  <si>
+    <t>22-04-2024</t>
+  </si>
+  <si>
+    <t>23-04-2024</t>
+  </si>
+  <si>
+    <t>24-04-2024</t>
+  </si>
+  <si>
+    <t>25-04-2024</t>
+  </si>
+  <si>
+    <t>26-04-2024</t>
+  </si>
+  <si>
+    <t>27-04-2024</t>
+  </si>
+  <si>
+    <t>28-04-2024</t>
+  </si>
+  <si>
+    <t>29-04-2024</t>
+  </si>
+  <si>
+    <t>30-04-2024</t>
+  </si>
+  <si>
+    <t>13-05-2024</t>
+  </si>
+  <si>
+    <t>14-05-2024</t>
+  </si>
+  <si>
+    <t>15-05-2024</t>
+  </si>
+  <si>
+    <t>16-05-2024</t>
+  </si>
+  <si>
+    <t>17-05-2024</t>
+  </si>
+  <si>
+    <t>18-05-2024</t>
+  </si>
+  <si>
+    <t>19-05-2024</t>
+  </si>
+  <si>
+    <t>20-05-2024</t>
+  </si>
+  <si>
+    <t>21-05-2024</t>
+  </si>
+  <si>
+    <t>22-05-2024</t>
+  </si>
+  <si>
+    <t>23-05-2024</t>
+  </si>
+  <si>
+    <t>24-05-2024</t>
+  </si>
+  <si>
+    <t>25-05-2024</t>
+  </si>
+  <si>
+    <t>26-05-2024</t>
+  </si>
+  <si>
+    <t>27-05-2024</t>
+  </si>
+  <si>
+    <t>28-05-2024</t>
+  </si>
+  <si>
+    <t>29-05-2024</t>
+  </si>
+  <si>
+    <t>30-05-2024</t>
+  </si>
+  <si>
+    <t>31-05-2024</t>
+  </si>
+  <si>
+    <t>13-06-2024</t>
+  </si>
+  <si>
+    <t>14-06-2024</t>
+  </si>
+  <si>
+    <t>15-06-2024</t>
+  </si>
+  <si>
+    <t>16-06-2024</t>
+  </si>
+  <si>
+    <t>17-06-2024</t>
+  </si>
+  <si>
+    <t>18-06-2024</t>
+  </si>
+  <si>
+    <t>19-06-2024</t>
+  </si>
+  <si>
+    <t>20-06-2024</t>
+  </si>
+  <si>
+    <t>21-06-2024</t>
+  </si>
+  <si>
+    <t>22-06-2024</t>
+  </si>
+  <si>
+    <t>23-06-2024</t>
+  </si>
+  <si>
+    <t>24-06-2024</t>
+  </si>
+  <si>
+    <t>25-06-2024</t>
+  </si>
+  <si>
+    <t>26-06-2024</t>
+  </si>
+  <si>
+    <t>27-06-2024</t>
+  </si>
+  <si>
+    <t>28-06-2024</t>
+  </si>
+  <si>
+    <t>29-06-2024</t>
+  </si>
+  <si>
+    <t>30-06-2024</t>
+  </si>
+  <si>
+    <t>13-07-2024</t>
+  </si>
+  <si>
+    <t>14-07-2024</t>
+  </si>
+  <si>
+    <t>15-07-2024</t>
+  </si>
+  <si>
+    <t>16-07-2024</t>
+  </si>
+  <si>
+    <t>17-07-2024</t>
+  </si>
+  <si>
+    <t>18-07-2024</t>
+  </si>
+  <si>
+    <t>19-07-2024</t>
+  </si>
+  <si>
+    <t>20-07-2024</t>
+  </si>
+  <si>
+    <t>21-07-2024</t>
+  </si>
+  <si>
+    <t>22-07-2024</t>
+  </si>
+  <si>
+    <t>23-07-2024</t>
+  </si>
+  <si>
+    <t>24-07-2024</t>
+  </si>
+  <si>
+    <t>25-07-2024</t>
+  </si>
+  <si>
+    <t>26-07-2024</t>
+  </si>
+  <si>
+    <t>27-07-2024</t>
+  </si>
+  <si>
+    <t>28-07-2024</t>
+  </si>
+  <si>
+    <t>29-07-2024</t>
+  </si>
+  <si>
+    <t>30-07-2024</t>
+  </si>
+  <si>
+    <t>31-07-2024</t>
+  </si>
+  <si>
+    <t>13-08-2024</t>
+  </si>
+  <si>
+    <t>14-08-2024</t>
+  </si>
+  <si>
+    <t>15-08-2024</t>
+  </si>
+  <si>
+    <t>16-08-2024</t>
+  </si>
+  <si>
+    <t>17-08-2024</t>
+  </si>
+  <si>
+    <t>18-08-2024</t>
+  </si>
+  <si>
+    <t>19-08-2024</t>
+  </si>
+  <si>
+    <t>20-08-2024</t>
+  </si>
+  <si>
+    <t>21-08-2024</t>
+  </si>
+  <si>
+    <t>22-08-2024</t>
+  </si>
+  <si>
+    <t>23-08-2024</t>
+  </si>
+  <si>
+    <t>24-08-2024</t>
+  </si>
+  <si>
+    <t>25-08-2024</t>
+  </si>
+  <si>
+    <t>26-08-2024</t>
+  </si>
+  <si>
+    <t>27-08-2024</t>
+  </si>
+  <si>
+    <t>28-08-2024</t>
+  </si>
+  <si>
+    <t>29-08-2024</t>
+  </si>
+  <si>
+    <t>30-08-2024</t>
+  </si>
+  <si>
+    <t>31-08-2024</t>
+  </si>
+  <si>
+    <t>13-09-2024</t>
+  </si>
+  <si>
+    <t>14-09-2024</t>
+  </si>
+  <si>
+    <t>15-09-2024</t>
+  </si>
+  <si>
+    <t>16-09-2024</t>
+  </si>
+  <si>
+    <t>17-09-2024</t>
+  </si>
+  <si>
+    <t>18-09-2024</t>
+  </si>
+  <si>
+    <t>19-09-2024</t>
+  </si>
+  <si>
+    <t>20-09-2024</t>
+  </si>
+  <si>
+    <t>21-09-2024</t>
+  </si>
+  <si>
+    <t>22-09-2024</t>
+  </si>
+  <si>
+    <t>23-09-2024</t>
+  </si>
+  <si>
+    <t>24-09-2024</t>
+  </si>
+  <si>
+    <t>25-09-2024</t>
+  </si>
+  <si>
+    <t>26-09-2024</t>
+  </si>
+  <si>
+    <t>27-09-2024</t>
+  </si>
+  <si>
+    <t>28-09-2024</t>
+  </si>
+  <si>
+    <t>29-09-2024</t>
+  </si>
+  <si>
+    <t>30-09-2024</t>
+  </si>
+  <si>
+    <t>13-10-2024</t>
+  </si>
+  <si>
+    <t>14-10-2024</t>
+  </si>
+  <si>
+    <t>15-10-2024</t>
+  </si>
+  <si>
+    <t>16-10-2024</t>
+  </si>
+  <si>
+    <t>17-10-2024</t>
+  </si>
+  <si>
+    <t>18-10-2024</t>
+  </si>
+  <si>
+    <t>19-10-2024</t>
+  </si>
+  <si>
+    <t>20-10-2024</t>
+  </si>
+  <si>
+    <t>21-10-2024</t>
+  </si>
+  <si>
+    <t>22-10-2024</t>
+  </si>
+  <si>
+    <t>23-10-2024</t>
+  </si>
+  <si>
+    <t>24-10-2024</t>
+  </si>
+  <si>
+    <t>25-10-2024</t>
+  </si>
+  <si>
+    <t>26-10-2024</t>
+  </si>
+  <si>
+    <t>27-10-2024</t>
+  </si>
+  <si>
+    <t>28-10-2024</t>
+  </si>
+  <si>
+    <t>29-10-2024</t>
+  </si>
+  <si>
+    <t>30-10-2024</t>
+  </si>
+  <si>
+    <t>31-10-2024</t>
+  </si>
+  <si>
+    <t>13-11-2024</t>
+  </si>
+  <si>
+    <t>14-11-2024</t>
+  </si>
+  <si>
+    <t>15-11-2024</t>
+  </si>
+  <si>
+    <t>16-11-2024</t>
+  </si>
+  <si>
+    <t>17-11-2024</t>
+  </si>
+  <si>
+    <t>18-11-2024</t>
+  </si>
+  <si>
+    <t>19-11-2024</t>
+  </si>
+  <si>
+    <t>20-11-2024</t>
+  </si>
+  <si>
+    <t>21-11-2024</t>
+  </si>
+  <si>
+    <t>22-11-2024</t>
+  </si>
+  <si>
+    <t>23-11-2024</t>
+  </si>
+  <si>
+    <t>24-11-2024</t>
+  </si>
+  <si>
+    <t>25-11-2024</t>
+  </si>
+  <si>
+    <t>26-11-2024</t>
+  </si>
+  <si>
+    <t>27-11-2024</t>
+  </si>
+  <si>
+    <t>28-11-2024</t>
+  </si>
+  <si>
+    <t>29-11-2024</t>
+  </si>
+  <si>
+    <t>30-11-2024</t>
+  </si>
+  <si>
+    <t>13-12-2024</t>
+  </si>
+  <si>
+    <t>14-12-2024</t>
+  </si>
+  <si>
+    <t>15-12-2024</t>
+  </si>
+  <si>
+    <t>16-12-2024</t>
+  </si>
+  <si>
+    <t>17-12-2024</t>
+  </si>
+  <si>
+    <t>18-12-2024</t>
+  </si>
+  <si>
+    <t>19-12-2024</t>
+  </si>
+  <si>
+    <t>20-12-2024</t>
+  </si>
+  <si>
+    <t>21-12-2024</t>
+  </si>
+  <si>
+    <t>22-12-2024</t>
+  </si>
+  <si>
+    <t>23-12-2024</t>
+  </si>
+  <si>
+    <t>24-12-2024</t>
+  </si>
+  <si>
+    <t>25-12-2024</t>
+  </si>
+  <si>
+    <t>26-12-2024</t>
+  </si>
+  <si>
+    <t>27-12-2024</t>
+  </si>
+  <si>
+    <t>28-12-2024</t>
+  </si>
+  <si>
+    <t>29-12-2024</t>
+  </si>
+  <si>
+    <t>30-12-2024</t>
+  </si>
+  <si>
+    <t>31-12-2024</t>
   </si>
 </sst>
 </file>
@@ -11155,7 +12484,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -11206,6 +12535,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11486,8 +12816,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B3784"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:B4541"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.75"/>
     <col min="2" max="2" width="14" style="17"/>
@@ -41765,6 +43095,6062 @@
         <v>286162</v>
       </c>
     </row>
+    <row r="3785" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3785">
+        <v>2023</v>
+      </c>
+      <c r="B3785" s="17">
+        <v>184021856</v>
+      </c>
+    </row>
+    <row r="3786" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3786" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3786" s="17">
+        <v>15992455</v>
+      </c>
+    </row>
+    <row r="3787" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3787" s="18">
+        <v>44927</v>
+      </c>
+      <c r="B3787" s="17">
+        <v>251209</v>
+      </c>
+    </row>
+    <row r="3788" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3788" s="18">
+        <v>44958</v>
+      </c>
+      <c r="B3788" s="17">
+        <v>407066</v>
+      </c>
+    </row>
+    <row r="3789" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3789" s="18">
+        <v>44986</v>
+      </c>
+      <c r="B3789" s="17">
+        <v>503488</v>
+      </c>
+    </row>
+    <row r="3790" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3790" s="18">
+        <v>45017</v>
+      </c>
+      <c r="B3790" s="17">
+        <v>576027</v>
+      </c>
+    </row>
+    <row r="3791" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3791" s="18">
+        <v>45047</v>
+      </c>
+      <c r="B3791" s="17">
+        <v>577789</v>
+      </c>
+    </row>
+    <row r="3792" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3792" s="18">
+        <v>45078</v>
+      </c>
+      <c r="B3792" s="17">
+        <v>620914</v>
+      </c>
+    </row>
+    <row r="3793" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3793" s="18">
+        <v>45108</v>
+      </c>
+      <c r="B3793" s="17">
+        <v>379281</v>
+      </c>
+    </row>
+    <row r="3794" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3794" s="18">
+        <v>45139</v>
+      </c>
+      <c r="B3794" s="17">
+        <v>265662</v>
+      </c>
+    </row>
+    <row r="3795" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3795" s="18">
+        <v>45170</v>
+      </c>
+      <c r="B3795" s="17">
+        <v>575639</v>
+      </c>
+    </row>
+    <row r="3796" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3796" s="18">
+        <v>45200</v>
+      </c>
+      <c r="B3796" s="17">
+        <v>594819</v>
+      </c>
+    </row>
+    <row r="3797" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3797" s="18">
+        <v>45231</v>
+      </c>
+      <c r="B3797" s="17">
+        <v>610327</v>
+      </c>
+    </row>
+    <row r="3798" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3798" s="18">
+        <v>45261</v>
+      </c>
+      <c r="B3798" s="17">
+        <v>613331</v>
+      </c>
+    </row>
+    <row r="3799" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3799" t="s">
+        <v>3677</v>
+      </c>
+      <c r="B3799" s="17">
+        <v>650957</v>
+      </c>
+    </row>
+    <row r="3800" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3800" t="s">
+        <v>3678</v>
+      </c>
+      <c r="B3800" s="17">
+        <v>416375</v>
+      </c>
+    </row>
+    <row r="3801" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3801" t="s">
+        <v>3679</v>
+      </c>
+      <c r="B3801" s="17">
+        <v>278943</v>
+      </c>
+    </row>
+    <row r="3802" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3802" t="s">
+        <v>3680</v>
+      </c>
+      <c r="B3802" s="17">
+        <v>579237</v>
+      </c>
+    </row>
+    <row r="3803" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3803" t="s">
+        <v>3681</v>
+      </c>
+      <c r="B3803" s="17">
+        <v>633218</v>
+      </c>
+    </row>
+    <row r="3804" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3804" t="s">
+        <v>3682</v>
+      </c>
+      <c r="B3804" s="17">
+        <v>606263</v>
+      </c>
+    </row>
+    <row r="3805" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3805" t="s">
+        <v>3683</v>
+      </c>
+      <c r="B3805" s="17">
+        <v>623587</v>
+      </c>
+    </row>
+    <row r="3806" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3806" t="s">
+        <v>3684</v>
+      </c>
+      <c r="B3806" s="17">
+        <v>651000</v>
+      </c>
+    </row>
+    <row r="3807" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3807" t="s">
+        <v>3685</v>
+      </c>
+      <c r="B3807" s="17">
+        <v>419838</v>
+      </c>
+    </row>
+    <row r="3808" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3808" t="s">
+        <v>3686</v>
+      </c>
+      <c r="B3808" s="17">
+        <v>281219</v>
+      </c>
+    </row>
+    <row r="3809" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3809" t="s">
+        <v>3687</v>
+      </c>
+      <c r="B3809" s="17">
+        <v>563052</v>
+      </c>
+    </row>
+    <row r="3810" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3810" t="s">
+        <v>3688</v>
+      </c>
+      <c r="B3810" s="17">
+        <v>589108</v>
+      </c>
+    </row>
+    <row r="3811" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3811" t="s">
+        <v>3689</v>
+      </c>
+      <c r="B3811" s="17">
+        <v>594892</v>
+      </c>
+    </row>
+    <row r="3812" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3812" t="s">
+        <v>3690</v>
+      </c>
+      <c r="B3812" s="17">
+        <v>610039</v>
+      </c>
+    </row>
+    <row r="3813" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3813" t="s">
+        <v>3691</v>
+      </c>
+      <c r="B3813" s="17">
+        <v>641543</v>
+      </c>
+    </row>
+    <row r="3814" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3814" t="s">
+        <v>3692</v>
+      </c>
+      <c r="B3814" s="17">
+        <v>402795</v>
+      </c>
+    </row>
+    <row r="3815" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3815" t="s">
+        <v>3693</v>
+      </c>
+      <c r="B3815" s="17">
+        <v>278619</v>
+      </c>
+    </row>
+    <row r="3816" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3816" t="s">
+        <v>3694</v>
+      </c>
+      <c r="B3816" s="17">
+        <v>578339</v>
+      </c>
+    </row>
+    <row r="3817" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3817" t="s">
+        <v>3695</v>
+      </c>
+      <c r="B3817" s="17">
+        <v>617879</v>
+      </c>
+    </row>
+    <row r="3818" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3818" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3818" s="17">
+        <v>14607364</v>
+      </c>
+    </row>
+    <row r="3819" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3819" s="18">
+        <v>44928</v>
+      </c>
+      <c r="B3819" s="17">
+        <v>631649</v>
+      </c>
+    </row>
+    <row r="3820" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3820" s="18">
+        <v>44959</v>
+      </c>
+      <c r="B3820" s="17">
+        <v>635930</v>
+      </c>
+    </row>
+    <row r="3821" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3821" s="18">
+        <v>44987</v>
+      </c>
+      <c r="B3821" s="17">
+        <v>703621</v>
+      </c>
+    </row>
+    <row r="3822" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3822" s="18">
+        <v>45018</v>
+      </c>
+      <c r="B3822" s="17">
+        <v>441314</v>
+      </c>
+    </row>
+    <row r="3823" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3823" s="18">
+        <v>45048</v>
+      </c>
+      <c r="B3823" s="17">
+        <v>296233</v>
+      </c>
+    </row>
+    <row r="3824" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3824" s="18">
+        <v>45079</v>
+      </c>
+      <c r="B3824" s="17">
+        <v>587333</v>
+      </c>
+    </row>
+    <row r="3825" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3825" s="18">
+        <v>45109</v>
+      </c>
+      <c r="B3825" s="17">
+        <v>609018</v>
+      </c>
+    </row>
+    <row r="3826" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3826" s="18">
+        <v>45140</v>
+      </c>
+      <c r="B3826" s="17">
+        <v>615097</v>
+      </c>
+    </row>
+    <row r="3827" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3827" s="18">
+        <v>45171</v>
+      </c>
+      <c r="B3827" s="17">
+        <v>622247</v>
+      </c>
+    </row>
+    <row r="3828" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3828" s="18">
+        <v>45201</v>
+      </c>
+      <c r="B3828" s="17">
+        <v>645855</v>
+      </c>
+    </row>
+    <row r="3829" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3829" s="18">
+        <v>45232</v>
+      </c>
+      <c r="B3829" s="17">
+        <v>414786</v>
+      </c>
+    </row>
+    <row r="3830" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3830" s="18">
+        <v>45262</v>
+      </c>
+      <c r="B3830" s="17">
+        <v>285722</v>
+      </c>
+    </row>
+    <row r="3831" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3831" t="s">
+        <v>3696</v>
+      </c>
+      <c r="B3831" s="17">
+        <v>470181</v>
+      </c>
+    </row>
+    <row r="3832" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3832" t="s">
+        <v>3697</v>
+      </c>
+      <c r="B3832" s="17">
+        <v>510949</v>
+      </c>
+    </row>
+    <row r="3833" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3833" t="s">
+        <v>3698</v>
+      </c>
+      <c r="B3833" s="17">
+        <v>498030</v>
+      </c>
+    </row>
+    <row r="3834" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3834" t="s">
+        <v>3699</v>
+      </c>
+      <c r="B3834" s="17">
+        <v>512074</v>
+      </c>
+    </row>
+    <row r="3835" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3835" t="s">
+        <v>3700</v>
+      </c>
+      <c r="B3835" s="17">
+        <v>516653</v>
+      </c>
+    </row>
+    <row r="3836" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3836" t="s">
+        <v>3701</v>
+      </c>
+      <c r="B3836" s="17">
+        <v>410883</v>
+      </c>
+    </row>
+    <row r="3837" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3837" t="s">
+        <v>3702</v>
+      </c>
+      <c r="B3837" s="17">
+        <v>294547</v>
+      </c>
+    </row>
+    <row r="3838" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3838" t="s">
+        <v>3703</v>
+      </c>
+      <c r="B3838" s="17">
+        <v>562050</v>
+      </c>
+    </row>
+    <row r="3839" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3839" t="s">
+        <v>3704</v>
+      </c>
+      <c r="B3839" s="17">
+        <v>578131</v>
+      </c>
+    </row>
+    <row r="3840" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3840" t="s">
+        <v>3705</v>
+      </c>
+      <c r="B3840" s="17">
+        <v>579853</v>
+      </c>
+    </row>
+    <row r="3841" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3841" t="s">
+        <v>3706</v>
+      </c>
+      <c r="B3841" s="17">
+        <v>602543</v>
+      </c>
+    </row>
+    <row r="3842" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3842" t="s">
+        <v>3707</v>
+      </c>
+      <c r="B3842" s="17">
+        <v>656729</v>
+      </c>
+    </row>
+    <row r="3843" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3843" t="s">
+        <v>3708</v>
+      </c>
+      <c r="B3843" s="17">
+        <v>423258</v>
+      </c>
+    </row>
+    <row r="3844" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3844" t="s">
+        <v>3709</v>
+      </c>
+      <c r="B3844" s="17">
+        <v>312188</v>
+      </c>
+    </row>
+    <row r="3845" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3845" t="s">
+        <v>3710</v>
+      </c>
+      <c r="B3845" s="17">
+        <v>576272</v>
+      </c>
+    </row>
+    <row r="3846" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3846" t="s">
+        <v>3711</v>
+      </c>
+      <c r="B3846" s="17">
+        <v>614218</v>
+      </c>
+    </row>
+    <row r="3847" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3847" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3847" s="17">
+        <v>17384844</v>
+      </c>
+    </row>
+    <row r="3848" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3848" s="18">
+        <v>44929</v>
+      </c>
+      <c r="B3848" s="17">
+        <v>625998</v>
+      </c>
+    </row>
+    <row r="3849" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3849" s="18">
+        <v>44960</v>
+      </c>
+      <c r="B3849" s="17">
+        <v>642750</v>
+      </c>
+    </row>
+    <row r="3850" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3850" s="18">
+        <v>44988</v>
+      </c>
+      <c r="B3850" s="17">
+        <v>676502</v>
+      </c>
+    </row>
+    <row r="3851" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3851" s="18">
+        <v>45019</v>
+      </c>
+      <c r="B3851" s="17">
+        <v>444625</v>
+      </c>
+    </row>
+    <row r="3852" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3852" s="18">
+        <v>45049</v>
+      </c>
+      <c r="B3852" s="17">
+        <v>319363</v>
+      </c>
+    </row>
+    <row r="3853" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3853" s="18">
+        <v>45080</v>
+      </c>
+      <c r="B3853" s="17">
+        <v>584107</v>
+      </c>
+    </row>
+    <row r="3854" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3854" s="18">
+        <v>45110</v>
+      </c>
+      <c r="B3854" s="17">
+        <v>616019</v>
+      </c>
+    </row>
+    <row r="3855" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3855" s="18">
+        <v>45141</v>
+      </c>
+      <c r="B3855" s="17">
+        <v>659290</v>
+      </c>
+    </row>
+    <row r="3856" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3856" s="18">
+        <v>45172</v>
+      </c>
+      <c r="B3856" s="17">
+        <v>641458</v>
+      </c>
+    </row>
+    <row r="3857" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3857" s="18">
+        <v>45202</v>
+      </c>
+      <c r="B3857" s="17">
+        <v>666923</v>
+      </c>
+    </row>
+    <row r="3858" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3858" s="18">
+        <v>45233</v>
+      </c>
+      <c r="B3858" s="17">
+        <v>428927</v>
+      </c>
+    </row>
+    <row r="3859" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3859" s="18">
+        <v>45263</v>
+      </c>
+      <c r="B3859" s="17">
+        <v>304788</v>
+      </c>
+    </row>
+    <row r="3860" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3860" t="s">
+        <v>3712</v>
+      </c>
+      <c r="B3860" s="17">
+        <v>610601</v>
+      </c>
+    </row>
+    <row r="3861" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3861" t="s">
+        <v>3713</v>
+      </c>
+      <c r="B3861" s="17">
+        <v>618273</v>
+      </c>
+    </row>
+    <row r="3862" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3862" t="s">
+        <v>3714</v>
+      </c>
+      <c r="B3862" s="17">
+        <v>613283</v>
+      </c>
+    </row>
+    <row r="3863" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3863" t="s">
+        <v>3715</v>
+      </c>
+      <c r="B3863" s="17">
+        <v>620210</v>
+      </c>
+    </row>
+    <row r="3864" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3864" t="s">
+        <v>3716</v>
+      </c>
+      <c r="B3864" s="17">
+        <v>663152</v>
+      </c>
+    </row>
+    <row r="3865" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3865" t="s">
+        <v>3717</v>
+      </c>
+      <c r="B3865" s="17">
+        <v>422774</v>
+      </c>
+    </row>
+    <row r="3866" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3866" t="s">
+        <v>3718</v>
+      </c>
+      <c r="B3866" s="17">
+        <v>306103</v>
+      </c>
+    </row>
+    <row r="3867" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3867" t="s">
+        <v>3719</v>
+      </c>
+      <c r="B3867" s="17">
+        <v>573988</v>
+      </c>
+    </row>
+    <row r="3868" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3868" t="s">
+        <v>3720</v>
+      </c>
+      <c r="B3868" s="17">
+        <v>602166</v>
+      </c>
+    </row>
+    <row r="3869" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3869" t="s">
+        <v>3721</v>
+      </c>
+      <c r="B3869" s="17">
+        <v>612017</v>
+      </c>
+    </row>
+    <row r="3870" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3870" t="s">
+        <v>3722</v>
+      </c>
+      <c r="B3870" s="17">
+        <v>635905</v>
+      </c>
+    </row>
+    <row r="3871" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3871" t="s">
+        <v>3723</v>
+      </c>
+      <c r="B3871" s="17">
+        <v>672535</v>
+      </c>
+    </row>
+    <row r="3872" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3872" t="s">
+        <v>3724</v>
+      </c>
+      <c r="B3872" s="17">
+        <v>429263</v>
+      </c>
+    </row>
+    <row r="3873" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3873" t="s">
+        <v>3725</v>
+      </c>
+      <c r="B3873" s="17">
+        <v>286972</v>
+      </c>
+    </row>
+    <row r="3874" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3874" t="s">
+        <v>3726</v>
+      </c>
+      <c r="B3874" s="17">
+        <v>566900</v>
+      </c>
+    </row>
+    <row r="3875" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3875" t="s">
+        <v>3727</v>
+      </c>
+      <c r="B3875" s="17">
+        <v>613540</v>
+      </c>
+    </row>
+    <row r="3876" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3876" t="s">
+        <v>3728</v>
+      </c>
+      <c r="B3876" s="17">
+        <v>605657</v>
+      </c>
+    </row>
+    <row r="3877" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3877" t="s">
+        <v>3729</v>
+      </c>
+      <c r="B3877" s="17">
+        <v>645248</v>
+      </c>
+    </row>
+    <row r="3878" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3878" t="s">
+        <v>3730</v>
+      </c>
+      <c r="B3878" s="17">
+        <v>675507</v>
+      </c>
+    </row>
+    <row r="3879" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3879" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3879" s="17">
+        <v>14553705</v>
+      </c>
+    </row>
+    <row r="3880" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3880" s="18">
+        <v>44930</v>
+      </c>
+      <c r="B3880" s="17">
+        <v>439020</v>
+      </c>
+    </row>
+    <row r="3881" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3881" s="18">
+        <v>44961</v>
+      </c>
+      <c r="B3881" s="17">
+        <v>325803</v>
+      </c>
+    </row>
+    <row r="3882" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3882" s="18">
+        <v>44989</v>
+      </c>
+      <c r="B3882" s="17">
+        <v>448330</v>
+      </c>
+    </row>
+    <row r="3883" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3883" s="18">
+        <v>45020</v>
+      </c>
+      <c r="B3883" s="17">
+        <v>450942</v>
+      </c>
+    </row>
+    <row r="3884" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3884" s="18">
+        <v>45050</v>
+      </c>
+      <c r="B3884" s="17">
+        <v>457009</v>
+      </c>
+    </row>
+    <row r="3885" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3885" s="18">
+        <v>45081</v>
+      </c>
+      <c r="B3885" s="17">
+        <v>293360</v>
+      </c>
+    </row>
+    <row r="3886" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3886" s="18">
+        <v>45111</v>
+      </c>
+      <c r="B3886" s="17">
+        <v>278115</v>
+      </c>
+    </row>
+    <row r="3887" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3887" s="18">
+        <v>45142</v>
+      </c>
+      <c r="B3887" s="17">
+        <v>361698</v>
+      </c>
+    </row>
+    <row r="3888" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3888" s="18">
+        <v>45173</v>
+      </c>
+      <c r="B3888" s="17">
+        <v>271529</v>
+      </c>
+    </row>
+    <row r="3889" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3889" s="18">
+        <v>45203</v>
+      </c>
+      <c r="B3889" s="17">
+        <v>249041</v>
+      </c>
+    </row>
+    <row r="3890" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3890" s="18">
+        <v>45234</v>
+      </c>
+      <c r="B3890" s="17">
+        <v>619395</v>
+      </c>
+    </row>
+    <row r="3891" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3891" s="18">
+        <v>45264</v>
+      </c>
+      <c r="B3891" s="17">
+        <v>598586</v>
+      </c>
+    </row>
+    <row r="3892" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3892" t="s">
+        <v>3731</v>
+      </c>
+      <c r="B3892" s="17">
+        <v>618508</v>
+      </c>
+    </row>
+    <row r="3893" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3893" t="s">
+        <v>3732</v>
+      </c>
+      <c r="B3893" s="17">
+        <v>659631</v>
+      </c>
+    </row>
+    <row r="3894" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3894" t="s">
+        <v>3733</v>
+      </c>
+      <c r="B3894" s="17">
+        <v>433426</v>
+      </c>
+    </row>
+    <row r="3895" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3895" t="s">
+        <v>3734</v>
+      </c>
+      <c r="B3895" s="17">
+        <v>320898</v>
+      </c>
+    </row>
+    <row r="3896" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3896" t="s">
+        <v>3735</v>
+      </c>
+      <c r="B3896" s="17">
+        <v>574259</v>
+      </c>
+    </row>
+    <row r="3897" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3897" t="s">
+        <v>3736</v>
+      </c>
+      <c r="B3897" s="17">
+        <v>598663</v>
+      </c>
+    </row>
+    <row r="3898" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3898" t="s">
+        <v>3737</v>
+      </c>
+      <c r="B3898" s="17">
+        <v>594817</v>
+      </c>
+    </row>
+    <row r="3899" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3899" t="s">
+        <v>3738</v>
+      </c>
+      <c r="B3899" s="17">
+        <v>618568</v>
+      </c>
+    </row>
+    <row r="3900" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3900" t="s">
+        <v>3739</v>
+      </c>
+      <c r="B3900" s="17">
+        <v>654844</v>
+      </c>
+    </row>
+    <row r="3901" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3901" t="s">
+        <v>3740</v>
+      </c>
+      <c r="B3901" s="17">
+        <v>458758</v>
+      </c>
+    </row>
+    <row r="3902" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3902" t="s">
+        <v>3741</v>
+      </c>
+      <c r="B3902" s="17">
+        <v>296069</v>
+      </c>
+    </row>
+    <row r="3903" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3903" t="s">
+        <v>3742</v>
+      </c>
+      <c r="B3903" s="17">
+        <v>583977</v>
+      </c>
+    </row>
+    <row r="3904" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3904" t="s">
+        <v>3743</v>
+      </c>
+      <c r="B3904" s="17">
+        <v>608442</v>
+      </c>
+    </row>
+    <row r="3905" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3905" t="s">
+        <v>3744</v>
+      </c>
+      <c r="B3905" s="17">
+        <v>624082</v>
+      </c>
+    </row>
+    <row r="3906" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3906" t="s">
+        <v>3745</v>
+      </c>
+      <c r="B3906" s="17">
+        <v>626737</v>
+      </c>
+    </row>
+    <row r="3907" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3907" t="s">
+        <v>3746</v>
+      </c>
+      <c r="B3907" s="17">
+        <v>680399</v>
+      </c>
+    </row>
+    <row r="3908" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3908" t="s">
+        <v>3747</v>
+      </c>
+      <c r="B3908" s="17">
+        <v>466487</v>
+      </c>
+    </row>
+    <row r="3909" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3909" t="s">
+        <v>3748</v>
+      </c>
+      <c r="B3909" s="17">
+        <v>342312</v>
+      </c>
+    </row>
+    <row r="3910" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3910" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3910" s="17">
+        <v>15615425</v>
+      </c>
+    </row>
+    <row r="3911" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3911" s="18">
+        <v>44931</v>
+      </c>
+      <c r="B3911" s="17">
+        <v>540101</v>
+      </c>
+    </row>
+    <row r="3912" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3912" s="18">
+        <v>44962</v>
+      </c>
+      <c r="B3912" s="17">
+        <v>597255</v>
+      </c>
+    </row>
+    <row r="3913" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3913" s="18">
+        <v>44990</v>
+      </c>
+      <c r="B3913" s="17">
+        <v>598150</v>
+      </c>
+    </row>
+    <row r="3914" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3914" s="18">
+        <v>45021</v>
+      </c>
+      <c r="B3914" s="17">
+        <v>670007</v>
+      </c>
+    </row>
+    <row r="3915" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3915" s="18">
+        <v>45051</v>
+      </c>
+      <c r="B3915" s="17">
+        <v>352472</v>
+      </c>
+    </row>
+    <row r="3916" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3916" s="18">
+        <v>45082</v>
+      </c>
+      <c r="B3916" s="17">
+        <v>405984</v>
+      </c>
+    </row>
+    <row r="3917" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3917" s="18">
+        <v>45112</v>
+      </c>
+      <c r="B3917" s="17">
+        <v>311126</v>
+      </c>
+    </row>
+    <row r="3918" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3918" s="18">
+        <v>45143</v>
+      </c>
+      <c r="B3918" s="17">
+        <v>561861</v>
+      </c>
+    </row>
+    <row r="3919" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3919" s="18">
+        <v>45174</v>
+      </c>
+      <c r="B3919" s="17">
+        <v>592372</v>
+      </c>
+    </row>
+    <row r="3920" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3920" s="18">
+        <v>45204</v>
+      </c>
+      <c r="B3920" s="17">
+        <v>601702</v>
+      </c>
+    </row>
+    <row r="3921" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3921" s="18">
+        <v>45235</v>
+      </c>
+      <c r="B3921" s="17">
+        <v>607365</v>
+      </c>
+    </row>
+    <row r="3922" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3922" s="18">
+        <v>45265</v>
+      </c>
+      <c r="B3922" s="17">
+        <v>650970</v>
+      </c>
+    </row>
+    <row r="3923" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3923" t="s">
+        <v>3749</v>
+      </c>
+      <c r="B3923" s="17">
+        <v>437421</v>
+      </c>
+    </row>
+    <row r="3924" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3924" t="s">
+        <v>3750</v>
+      </c>
+      <c r="B3924" s="17">
+        <v>355523</v>
+      </c>
+    </row>
+    <row r="3925" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3925" t="s">
+        <v>3751</v>
+      </c>
+      <c r="B3925" s="17">
+        <v>548803</v>
+      </c>
+    </row>
+    <row r="3926" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3926" t="s">
+        <v>3752</v>
+      </c>
+      <c r="B3926" s="17">
+        <v>587686</v>
+      </c>
+    </row>
+    <row r="3927" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3927" t="s">
+        <v>3753</v>
+      </c>
+      <c r="B3927" s="17">
+        <v>650061</v>
+      </c>
+    </row>
+    <row r="3928" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3928" t="s">
+        <v>3754</v>
+      </c>
+      <c r="B3928" s="17">
+        <v>324316</v>
+      </c>
+    </row>
+    <row r="3929" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3929" t="s">
+        <v>3755</v>
+      </c>
+      <c r="B3929" s="17">
+        <v>451568</v>
+      </c>
+    </row>
+    <row r="3930" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3930" t="s">
+        <v>3756</v>
+      </c>
+      <c r="B3930" s="17">
+        <v>396349</v>
+      </c>
+    </row>
+    <row r="3931" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3931" t="s">
+        <v>3757</v>
+      </c>
+      <c r="B3931" s="17">
+        <v>300919</v>
+      </c>
+    </row>
+    <row r="3932" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3932" t="s">
+        <v>3758</v>
+      </c>
+      <c r="B3932" s="17">
+        <v>543548</v>
+      </c>
+    </row>
+    <row r="3933" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3933" t="s">
+        <v>3759</v>
+      </c>
+      <c r="B3933" s="17">
+        <v>584968</v>
+      </c>
+    </row>
+    <row r="3934" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3934" t="s">
+        <v>3760</v>
+      </c>
+      <c r="B3934" s="17">
+        <v>568872</v>
+      </c>
+    </row>
+    <row r="3935" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3935" t="s">
+        <v>3761</v>
+      </c>
+      <c r="B3935" s="17">
+        <v>583413</v>
+      </c>
+    </row>
+    <row r="3936" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3936" t="s">
+        <v>3762</v>
+      </c>
+      <c r="B3936" s="17">
+        <v>614444</v>
+      </c>
+    </row>
+    <row r="3937" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3937" t="s">
+        <v>3763</v>
+      </c>
+      <c r="B3937" s="17">
+        <v>411425</v>
+      </c>
+    </row>
+    <row r="3938" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3938" t="s">
+        <v>3764</v>
+      </c>
+      <c r="B3938" s="17">
+        <v>295958</v>
+      </c>
+    </row>
+    <row r="3939" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3939" t="s">
+        <v>3765</v>
+      </c>
+      <c r="B3939" s="17">
+        <v>318462</v>
+      </c>
+    </row>
+    <row r="3940" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3940" t="s">
+        <v>3766</v>
+      </c>
+      <c r="B3940" s="17">
+        <v>560719</v>
+      </c>
+    </row>
+    <row r="3941" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3941" t="s">
+        <v>3767</v>
+      </c>
+      <c r="B3941" s="17">
+        <v>591605</v>
+      </c>
+    </row>
+    <row r="3942" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3942" t="s">
+        <v>160</v>
+      </c>
+      <c r="B3942" s="17">
+        <v>15216070</v>
+      </c>
+    </row>
+    <row r="3943" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3943" s="18">
+        <v>44932</v>
+      </c>
+      <c r="B3943" s="17">
+        <v>633370</v>
+      </c>
+    </row>
+    <row r="3944" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3944" s="18">
+        <v>44963</v>
+      </c>
+      <c r="B3944" s="17">
+        <v>657328</v>
+      </c>
+    </row>
+    <row r="3945" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3945" s="18">
+        <v>44991</v>
+      </c>
+      <c r="B3945" s="17">
+        <v>451724</v>
+      </c>
+    </row>
+    <row r="3946" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3946" s="18">
+        <v>45022</v>
+      </c>
+      <c r="B3946" s="17">
+        <v>357558</v>
+      </c>
+    </row>
+    <row r="3947" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3947" s="18">
+        <v>45052</v>
+      </c>
+      <c r="B3947" s="17">
+        <v>326279</v>
+      </c>
+    </row>
+    <row r="3948" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3948" s="18">
+        <v>45083</v>
+      </c>
+      <c r="B3948" s="17">
+        <v>567393</v>
+      </c>
+    </row>
+    <row r="3949" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3949" s="18">
+        <v>45113</v>
+      </c>
+      <c r="B3949" s="17">
+        <v>575088</v>
+      </c>
+    </row>
+    <row r="3950" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3950" s="18">
+        <v>45144</v>
+      </c>
+      <c r="B3950" s="17">
+        <v>595248</v>
+      </c>
+    </row>
+    <row r="3951" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3951" s="18">
+        <v>45175</v>
+      </c>
+      <c r="B3951" s="17">
+        <v>643254</v>
+      </c>
+    </row>
+    <row r="3952" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3952" s="18">
+        <v>45205</v>
+      </c>
+      <c r="B3952" s="17">
+        <v>457674</v>
+      </c>
+    </row>
+    <row r="3953" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3953" s="18">
+        <v>45236</v>
+      </c>
+      <c r="B3953" s="17">
+        <v>315669</v>
+      </c>
+    </row>
+    <row r="3954" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3954" s="18">
+        <v>45266</v>
+      </c>
+      <c r="B3954" s="17">
+        <v>522395</v>
+      </c>
+    </row>
+    <row r="3955" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3955" t="s">
+        <v>3768</v>
+      </c>
+      <c r="B3955" s="17">
+        <v>555722</v>
+      </c>
+    </row>
+    <row r="3956" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3956" t="s">
+        <v>3769</v>
+      </c>
+      <c r="B3956" s="17">
+        <v>563735</v>
+      </c>
+    </row>
+    <row r="3957" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3957" t="s">
+        <v>3770</v>
+      </c>
+      <c r="B3957" s="17">
+        <v>572978</v>
+      </c>
+    </row>
+    <row r="3958" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3958" t="s">
+        <v>3771</v>
+      </c>
+      <c r="B3958" s="17">
+        <v>633769</v>
+      </c>
+    </row>
+    <row r="3959" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3959" t="s">
+        <v>3772</v>
+      </c>
+      <c r="B3959" s="17">
+        <v>427187</v>
+      </c>
+    </row>
+    <row r="3960" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3960" t="s">
+        <v>3773</v>
+      </c>
+      <c r="B3960" s="17">
+        <v>303733</v>
+      </c>
+    </row>
+    <row r="3961" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3961" t="s">
+        <v>3774</v>
+      </c>
+      <c r="B3961" s="17">
+        <v>543557</v>
+      </c>
+    </row>
+    <row r="3962" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3962" t="s">
+        <v>3775</v>
+      </c>
+      <c r="B3962" s="17">
+        <v>574416</v>
+      </c>
+    </row>
+    <row r="3963" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3963" t="s">
+        <v>3776</v>
+      </c>
+      <c r="B3963" s="17">
+        <v>584280</v>
+      </c>
+    </row>
+    <row r="3964" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3964" t="s">
+        <v>3777</v>
+      </c>
+      <c r="B3964" s="17">
+        <v>590037</v>
+      </c>
+    </row>
+    <row r="3965" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3965" t="s">
+        <v>3778</v>
+      </c>
+      <c r="B3965" s="17">
+        <v>583094</v>
+      </c>
+    </row>
+    <row r="3966" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3966" t="s">
+        <v>3779</v>
+      </c>
+      <c r="B3966" s="17">
+        <v>397952</v>
+      </c>
+    </row>
+    <row r="3967" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3967" t="s">
+        <v>3780</v>
+      </c>
+      <c r="B3967" s="17">
+        <v>295968</v>
+      </c>
+    </row>
+    <row r="3968" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3968" t="s">
+        <v>3781</v>
+      </c>
+      <c r="B3968" s="17">
+        <v>447851</v>
+      </c>
+    </row>
+    <row r="3969" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3969" t="s">
+        <v>3782</v>
+      </c>
+      <c r="B3969" s="17">
+        <v>519762</v>
+      </c>
+    </row>
+    <row r="3970" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3970" t="s">
+        <v>3783</v>
+      </c>
+      <c r="B3970" s="17">
+        <v>496146</v>
+      </c>
+    </row>
+    <row r="3971" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3971" t="s">
+        <v>3784</v>
+      </c>
+      <c r="B3971" s="17">
+        <v>484346</v>
+      </c>
+    </row>
+    <row r="3972" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3972" t="s">
+        <v>3785</v>
+      </c>
+      <c r="B3972" s="17">
+        <v>538557</v>
+      </c>
+    </row>
+    <row r="3973" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3973" t="s">
+        <v>191</v>
+      </c>
+      <c r="B3973" s="17">
+        <v>11645568</v>
+      </c>
+    </row>
+    <row r="3974" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3974" s="18">
+        <v>44933</v>
+      </c>
+      <c r="B3974" s="17">
+        <v>393347</v>
+      </c>
+    </row>
+    <row r="3975" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3975" s="18">
+        <v>44964</v>
+      </c>
+      <c r="B3975" s="17">
+        <v>302647</v>
+      </c>
+    </row>
+    <row r="3976" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3976" s="18">
+        <v>44992</v>
+      </c>
+      <c r="B3976" s="17">
+        <v>453231</v>
+      </c>
+    </row>
+    <row r="3977" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3977" s="18">
+        <v>45023</v>
+      </c>
+      <c r="B3977" s="17">
+        <v>468952</v>
+      </c>
+    </row>
+    <row r="3978" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3978" s="18">
+        <v>45053</v>
+      </c>
+      <c r="B3978" s="17">
+        <v>476553</v>
+      </c>
+    </row>
+    <row r="3979" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3979" s="18">
+        <v>45084</v>
+      </c>
+      <c r="B3979" s="17">
+        <v>493090</v>
+      </c>
+    </row>
+    <row r="3980" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3980" s="18">
+        <v>45114</v>
+      </c>
+      <c r="B3980" s="17">
+        <v>483829</v>
+      </c>
+    </row>
+    <row r="3981" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3981" s="18">
+        <v>45145</v>
+      </c>
+      <c r="B3981" s="17">
+        <v>379068</v>
+      </c>
+    </row>
+    <row r="3982" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3982" s="18">
+        <v>45176</v>
+      </c>
+      <c r="B3982" s="17">
+        <v>289301</v>
+      </c>
+    </row>
+    <row r="3983" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3983" s="18">
+        <v>45206</v>
+      </c>
+      <c r="B3983" s="17">
+        <v>361525</v>
+      </c>
+    </row>
+    <row r="3984" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3984" s="18">
+        <v>45237</v>
+      </c>
+      <c r="B3984" s="17">
+        <v>419085</v>
+      </c>
+    </row>
+    <row r="3985" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3985" s="18">
+        <v>45267</v>
+      </c>
+      <c r="B3985" s="17">
+        <v>393951</v>
+      </c>
+    </row>
+    <row r="3986" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3986" t="s">
+        <v>3786</v>
+      </c>
+      <c r="B3986" s="17">
+        <v>416102</v>
+      </c>
+    </row>
+    <row r="3987" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3987" t="s">
+        <v>3787</v>
+      </c>
+      <c r="B3987" s="17">
+        <v>423129</v>
+      </c>
+    </row>
+    <row r="3988" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3988" t="s">
+        <v>3788</v>
+      </c>
+      <c r="B3988" s="17">
+        <v>332889</v>
+      </c>
+    </row>
+    <row r="3989" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3989" t="s">
+        <v>3789</v>
+      </c>
+      <c r="B3989" s="17">
+        <v>250055</v>
+      </c>
+    </row>
+    <row r="3990" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3990" t="s">
+        <v>3790</v>
+      </c>
+      <c r="B3990" s="17">
+        <v>339481</v>
+      </c>
+    </row>
+    <row r="3991" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3991" t="s">
+        <v>3791</v>
+      </c>
+      <c r="B3991" s="17">
+        <v>360670</v>
+      </c>
+    </row>
+    <row r="3992" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3992" t="s">
+        <v>3792</v>
+      </c>
+      <c r="B3992" s="17">
+        <v>356298</v>
+      </c>
+    </row>
+    <row r="3993" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3993" t="s">
+        <v>3793</v>
+      </c>
+      <c r="B3993" s="17">
+        <v>382969</v>
+      </c>
+    </row>
+    <row r="3994" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3994" t="s">
+        <v>3794</v>
+      </c>
+      <c r="B3994" s="17">
+        <v>388122</v>
+      </c>
+    </row>
+    <row r="3995" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3995" t="s">
+        <v>3795</v>
+      </c>
+      <c r="B3995" s="17">
+        <v>328950</v>
+      </c>
+    </row>
+    <row r="3996" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3996" t="s">
+        <v>3796</v>
+      </c>
+      <c r="B3996" s="17">
+        <v>242279</v>
+      </c>
+    </row>
+    <row r="3997" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3997" t="s">
+        <v>3797</v>
+      </c>
+      <c r="B3997" s="17">
+        <v>341904</v>
+      </c>
+    </row>
+    <row r="3998" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3998" t="s">
+        <v>3798</v>
+      </c>
+      <c r="B3998" s="17">
+        <v>366117</v>
+      </c>
+    </row>
+    <row r="3999" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3999" t="s">
+        <v>3799</v>
+      </c>
+      <c r="B3999" s="17">
+        <v>378752</v>
+      </c>
+    </row>
+    <row r="4000" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4000" t="s">
+        <v>3800</v>
+      </c>
+      <c r="B4000" s="17">
+        <v>373094</v>
+      </c>
+    </row>
+    <row r="4001" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4001" t="s">
+        <v>3801</v>
+      </c>
+      <c r="B4001" s="17">
+        <v>417720</v>
+      </c>
+    </row>
+    <row r="4002" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4002" t="s">
+        <v>3802</v>
+      </c>
+      <c r="B4002" s="17">
+        <v>342537</v>
+      </c>
+    </row>
+    <row r="4003" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4003" t="s">
+        <v>3803</v>
+      </c>
+      <c r="B4003" s="17">
+        <v>282778</v>
+      </c>
+    </row>
+    <row r="4004" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4004" t="s">
+        <v>3804</v>
+      </c>
+      <c r="B4004" s="17">
+        <v>407143</v>
+      </c>
+    </row>
+    <row r="4005" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4005" t="s">
+        <v>223</v>
+      </c>
+      <c r="B4005" s="17">
+        <v>15393239</v>
+      </c>
+    </row>
+    <row r="4006" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4006" s="18">
+        <v>44934</v>
+      </c>
+      <c r="B4006" s="17">
+        <v>430863</v>
+      </c>
+    </row>
+    <row r="4007" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4007" s="18">
+        <v>44965</v>
+      </c>
+      <c r="B4007" s="17">
+        <v>446334</v>
+      </c>
+    </row>
+    <row r="4008" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4008" s="18">
+        <v>44993</v>
+      </c>
+      <c r="B4008" s="17">
+        <v>445629</v>
+      </c>
+    </row>
+    <row r="4009" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4009" s="18">
+        <v>45024</v>
+      </c>
+      <c r="B4009" s="17">
+        <v>480330</v>
+      </c>
+    </row>
+    <row r="4010" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4010" s="18">
+        <v>45054</v>
+      </c>
+      <c r="B4010" s="17">
+        <v>410150</v>
+      </c>
+    </row>
+    <row r="4011" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4011" s="18">
+        <v>45085</v>
+      </c>
+      <c r="B4011" s="17">
+        <v>298497</v>
+      </c>
+    </row>
+    <row r="4012" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4012" s="18">
+        <v>45115</v>
+      </c>
+      <c r="B4012" s="17">
+        <v>481472</v>
+      </c>
+    </row>
+    <row r="4013" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4013" s="18">
+        <v>45146</v>
+      </c>
+      <c r="B4013" s="17">
+        <v>518696</v>
+      </c>
+    </row>
+    <row r="4014" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4014" s="18">
+        <v>45177</v>
+      </c>
+      <c r="B4014" s="17">
+        <v>534375</v>
+      </c>
+    </row>
+    <row r="4015" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4015" s="18">
+        <v>45207</v>
+      </c>
+      <c r="B4015" s="17">
+        <v>535543</v>
+      </c>
+    </row>
+    <row r="4016" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4016" s="18">
+        <v>45238</v>
+      </c>
+      <c r="B4016" s="17">
+        <v>590816</v>
+      </c>
+    </row>
+    <row r="4017" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4017" s="18">
+        <v>45268</v>
+      </c>
+      <c r="B4017" s="17">
+        <v>399637</v>
+      </c>
+    </row>
+    <row r="4018" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4018" t="s">
+        <v>3805</v>
+      </c>
+      <c r="B4018" s="17">
+        <v>304980</v>
+      </c>
+    </row>
+    <row r="4019" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4019" t="s">
+        <v>3806</v>
+      </c>
+      <c r="B4019" s="17">
+        <v>514058</v>
+      </c>
+    </row>
+    <row r="4020" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4020" t="s">
+        <v>3807</v>
+      </c>
+      <c r="B4020" s="17">
+        <v>541741</v>
+      </c>
+    </row>
+    <row r="4021" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4021" t="s">
+        <v>3808</v>
+      </c>
+      <c r="B4021" s="17">
+        <v>557519</v>
+      </c>
+    </row>
+    <row r="4022" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4022" t="s">
+        <v>3809</v>
+      </c>
+      <c r="B4022" s="17">
+        <v>567325</v>
+      </c>
+    </row>
+    <row r="4023" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4023" t="s">
+        <v>3810</v>
+      </c>
+      <c r="B4023" s="17">
+        <v>631824</v>
+      </c>
+    </row>
+    <row r="4024" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4024" t="s">
+        <v>3811</v>
+      </c>
+      <c r="B4024" s="17">
+        <v>470544</v>
+      </c>
+    </row>
+    <row r="4025" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4025" t="s">
+        <v>3812</v>
+      </c>
+      <c r="B4025" s="17">
+        <v>313468</v>
+      </c>
+    </row>
+    <row r="4026" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4026" t="s">
+        <v>3813</v>
+      </c>
+      <c r="B4026" s="17">
+        <v>520914</v>
+      </c>
+    </row>
+    <row r="4027" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4027" t="s">
+        <v>3814</v>
+      </c>
+      <c r="B4027" s="17">
+        <v>551849</v>
+      </c>
+    </row>
+    <row r="4028" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4028" t="s">
+        <v>3815</v>
+      </c>
+      <c r="B4028" s="17">
+        <v>555675</v>
+      </c>
+    </row>
+    <row r="4029" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4029" t="s">
+        <v>3816</v>
+      </c>
+      <c r="B4029" s="17">
+        <v>575944</v>
+      </c>
+    </row>
+    <row r="4030" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4030" t="s">
+        <v>3817</v>
+      </c>
+      <c r="B4030" s="17">
+        <v>630567</v>
+      </c>
+    </row>
+    <row r="4031" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4031" t="s">
+        <v>3818</v>
+      </c>
+      <c r="B4031" s="17">
+        <v>437506</v>
+      </c>
+    </row>
+    <row r="4032" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4032" t="s">
+        <v>3819</v>
+      </c>
+      <c r="B4032" s="17">
+        <v>301123</v>
+      </c>
+    </row>
+    <row r="4033" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4033" t="s">
+        <v>3820</v>
+      </c>
+      <c r="B4033" s="17">
+        <v>547867</v>
+      </c>
+    </row>
+    <row r="4034" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4034" t="s">
+        <v>3821</v>
+      </c>
+      <c r="B4034" s="17">
+        <v>570417</v>
+      </c>
+    </row>
+    <row r="4035" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4035" t="s">
+        <v>3822</v>
+      </c>
+      <c r="B4035" s="17">
+        <v>593025</v>
+      </c>
+    </row>
+    <row r="4036" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4036" t="s">
+        <v>3823</v>
+      </c>
+      <c r="B4036" s="17">
+        <v>634551</v>
+      </c>
+    </row>
+    <row r="4037" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4037" t="s">
+        <v>255</v>
+      </c>
+      <c r="B4037" s="17">
+        <v>15994776</v>
+      </c>
+    </row>
+    <row r="4038" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4038" s="18">
+        <v>44935</v>
+      </c>
+      <c r="B4038" s="17">
+        <v>685381</v>
+      </c>
+    </row>
+    <row r="4039" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4039" s="18">
+        <v>44966</v>
+      </c>
+      <c r="B4039" s="17">
+        <v>465713</v>
+      </c>
+    </row>
+    <row r="4040" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4040" s="18">
+        <v>44994</v>
+      </c>
+      <c r="B4040" s="17">
+        <v>321177</v>
+      </c>
+    </row>
+    <row r="4041" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4041" s="18">
+        <v>45025</v>
+      </c>
+      <c r="B4041" s="17">
+        <v>552874</v>
+      </c>
+    </row>
+    <row r="4042" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4042" s="18">
+        <v>45055</v>
+      </c>
+      <c r="B4042" s="17">
+        <v>573745</v>
+      </c>
+    </row>
+    <row r="4043" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4043" s="18">
+        <v>45086</v>
+      </c>
+      <c r="B4043" s="17">
+        <v>576537</v>
+      </c>
+    </row>
+    <row r="4044" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4044" s="18">
+        <v>45116</v>
+      </c>
+      <c r="B4044" s="17">
+        <v>606830</v>
+      </c>
+    </row>
+    <row r="4045" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4045" s="18">
+        <v>45147</v>
+      </c>
+      <c r="B4045" s="17">
+        <v>641346</v>
+      </c>
+    </row>
+    <row r="4046" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4046" s="18">
+        <v>45178</v>
+      </c>
+      <c r="B4046" s="17">
+        <v>439812</v>
+      </c>
+    </row>
+    <row r="4047" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4047" s="18">
+        <v>45208</v>
+      </c>
+      <c r="B4047" s="17">
+        <v>312581</v>
+      </c>
+    </row>
+    <row r="4048" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4048" s="18">
+        <v>45239</v>
+      </c>
+      <c r="B4048" s="17">
+        <v>534748</v>
+      </c>
+    </row>
+    <row r="4049" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4049" s="18">
+        <v>45269</v>
+      </c>
+      <c r="B4049" s="17">
+        <v>576764</v>
+      </c>
+    </row>
+    <row r="4050" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4050" t="s">
+        <v>3824</v>
+      </c>
+      <c r="B4050" s="17">
+        <v>575341</v>
+      </c>
+    </row>
+    <row r="4051" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4051" t="s">
+        <v>3825</v>
+      </c>
+      <c r="B4051" s="17">
+        <v>588138</v>
+      </c>
+    </row>
+    <row r="4052" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4052" t="s">
+        <v>3826</v>
+      </c>
+      <c r="B4052" s="17">
+        <v>659205</v>
+      </c>
+    </row>
+    <row r="4053" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4053" t="s">
+        <v>3827</v>
+      </c>
+      <c r="B4053" s="17">
+        <v>445859</v>
+      </c>
+    </row>
+    <row r="4054" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4054" t="s">
+        <v>3828</v>
+      </c>
+      <c r="B4054" s="17">
+        <v>354272</v>
+      </c>
+    </row>
+    <row r="4055" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4055" t="s">
+        <v>3829</v>
+      </c>
+      <c r="B4055" s="17">
+        <v>551476</v>
+      </c>
+    </row>
+    <row r="4056" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4056" t="s">
+        <v>3830</v>
+      </c>
+      <c r="B4056" s="17">
+        <v>582661</v>
+      </c>
+    </row>
+    <row r="4057" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4057" t="s">
+        <v>3831</v>
+      </c>
+      <c r="B4057" s="17">
+        <v>593604</v>
+      </c>
+    </row>
+    <row r="4058" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4058" t="s">
+        <v>3832</v>
+      </c>
+      <c r="B4058" s="17">
+        <v>590266</v>
+      </c>
+    </row>
+    <row r="4059" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4059" t="s">
+        <v>3833</v>
+      </c>
+      <c r="B4059" s="17">
+        <v>648127</v>
+      </c>
+    </row>
+    <row r="4060" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4060" t="s">
+        <v>3834</v>
+      </c>
+      <c r="B4060" s="17">
+        <v>410627</v>
+      </c>
+    </row>
+    <row r="4061" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4061" t="s">
+        <v>3835</v>
+      </c>
+      <c r="B4061" s="17">
+        <v>301477</v>
+      </c>
+    </row>
+    <row r="4062" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4062" t="s">
+        <v>3836</v>
+      </c>
+      <c r="B4062" s="17">
+        <v>550495</v>
+      </c>
+    </row>
+    <row r="4063" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4063" t="s">
+        <v>3837</v>
+      </c>
+      <c r="B4063" s="17">
+        <v>574579</v>
+      </c>
+    </row>
+    <row r="4064" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4064" t="s">
+        <v>3838</v>
+      </c>
+      <c r="B4064" s="17">
+        <v>570260</v>
+      </c>
+    </row>
+    <row r="4065" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4065" t="s">
+        <v>3839</v>
+      </c>
+      <c r="B4065" s="17">
+        <v>584138</v>
+      </c>
+    </row>
+    <row r="4066" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4066" t="s">
+        <v>3840</v>
+      </c>
+      <c r="B4066" s="17">
+        <v>661565</v>
+      </c>
+    </row>
+    <row r="4067" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4067" t="s">
+        <v>3841</v>
+      </c>
+      <c r="B4067" s="17">
+        <v>465178</v>
+      </c>
+    </row>
+    <row r="4068" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4068" t="s">
+        <v>286</v>
+      </c>
+      <c r="B4068" s="17">
+        <v>15668884</v>
+      </c>
+    </row>
+    <row r="4069" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4069" s="18">
+        <v>44936</v>
+      </c>
+      <c r="B4069" s="17">
+        <v>313162</v>
+      </c>
+    </row>
+    <row r="4070" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4070" s="18">
+        <v>44967</v>
+      </c>
+      <c r="B4070" s="17">
+        <v>569616</v>
+      </c>
+    </row>
+    <row r="4071" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4071" s="18">
+        <v>44995</v>
+      </c>
+      <c r="B4071" s="17">
+        <v>612446</v>
+      </c>
+    </row>
+    <row r="4072" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4072" s="18">
+        <v>45026</v>
+      </c>
+      <c r="B4072" s="17">
+        <v>605008</v>
+      </c>
+    </row>
+    <row r="4073" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4073" s="18">
+        <v>45056</v>
+      </c>
+      <c r="B4073" s="17">
+        <v>606683</v>
+      </c>
+    </row>
+    <row r="4074" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4074" s="18">
+        <v>45087</v>
+      </c>
+      <c r="B4074" s="17">
+        <v>660392</v>
+      </c>
+    </row>
+    <row r="4075" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4075" s="18">
+        <v>45117</v>
+      </c>
+      <c r="B4075" s="17">
+        <v>426659</v>
+      </c>
+    </row>
+    <row r="4076" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4076" s="18">
+        <v>45148</v>
+      </c>
+      <c r="B4076" s="17">
+        <v>314889</v>
+      </c>
+    </row>
+    <row r="4077" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4077" s="18">
+        <v>45179</v>
+      </c>
+      <c r="B4077" s="17">
+        <v>544050</v>
+      </c>
+    </row>
+    <row r="4078" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4078" s="18">
+        <v>45209</v>
+      </c>
+      <c r="B4078" s="17">
+        <v>577342</v>
+      </c>
+    </row>
+    <row r="4079" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4079" s="18">
+        <v>45240</v>
+      </c>
+      <c r="B4079" s="17">
+        <v>584744</v>
+      </c>
+    </row>
+    <row r="4080" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4080" s="18">
+        <v>45270</v>
+      </c>
+      <c r="B4080" s="17">
+        <v>603565</v>
+      </c>
+    </row>
+    <row r="4081" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4081" t="s">
+        <v>3842</v>
+      </c>
+      <c r="B4081" s="17">
+        <v>616319</v>
+      </c>
+    </row>
+    <row r="4082" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4082" t="s">
+        <v>3843</v>
+      </c>
+      <c r="B4082" s="17">
+        <v>436300</v>
+      </c>
+    </row>
+    <row r="4083" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4083" t="s">
+        <v>3844</v>
+      </c>
+      <c r="B4083" s="17">
+        <v>304443</v>
+      </c>
+    </row>
+    <row r="4084" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4084" t="s">
+        <v>3845</v>
+      </c>
+      <c r="B4084" s="17">
+        <v>428623</v>
+      </c>
+    </row>
+    <row r="4085" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4085" t="s">
+        <v>3846</v>
+      </c>
+      <c r="B4085" s="17">
+        <v>444430</v>
+      </c>
+    </row>
+    <row r="4086" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4086" t="s">
+        <v>3847</v>
+      </c>
+      <c r="B4086" s="17">
+        <v>446435</v>
+      </c>
+    </row>
+    <row r="4087" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4087" t="s">
+        <v>3848</v>
+      </c>
+      <c r="B4087" s="17">
+        <v>462154</v>
+      </c>
+    </row>
+    <row r="4088" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4088" t="s">
+        <v>3849</v>
+      </c>
+      <c r="B4088" s="17">
+        <v>458329</v>
+      </c>
+    </row>
+    <row r="4089" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4089" t="s">
+        <v>3850</v>
+      </c>
+      <c r="B4089" s="17">
+        <v>376312</v>
+      </c>
+    </row>
+    <row r="4090" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4090" t="s">
+        <v>3851</v>
+      </c>
+      <c r="B4090" s="17">
+        <v>297235</v>
+      </c>
+    </row>
+    <row r="4091" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4091" t="s">
+        <v>3852</v>
+      </c>
+      <c r="B4091" s="17">
+        <v>539399</v>
+      </c>
+    </row>
+    <row r="4092" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4092" t="s">
+        <v>3853</v>
+      </c>
+      <c r="B4092" s="17">
+        <v>583136</v>
+      </c>
+    </row>
+    <row r="4093" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4093" t="s">
+        <v>3854</v>
+      </c>
+      <c r="B4093" s="17">
+        <v>623537</v>
+      </c>
+    </row>
+    <row r="4094" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4094" t="s">
+        <v>3855</v>
+      </c>
+      <c r="B4094" s="17">
+        <v>618713</v>
+      </c>
+    </row>
+    <row r="4095" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4095" t="s">
+        <v>3856</v>
+      </c>
+      <c r="B4095" s="17">
+        <v>660280</v>
+      </c>
+    </row>
+    <row r="4096" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4096" t="s">
+        <v>3857</v>
+      </c>
+      <c r="B4096" s="17">
+        <v>450847</v>
+      </c>
+    </row>
+    <row r="4097" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4097" t="s">
+        <v>3858</v>
+      </c>
+      <c r="B4097" s="17">
+        <v>295364</v>
+      </c>
+    </row>
+    <row r="4098" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4098" t="s">
+        <v>3859</v>
+      </c>
+      <c r="B4098" s="17">
+        <v>554028</v>
+      </c>
+    </row>
+    <row r="4099" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4099" t="s">
+        <v>3860</v>
+      </c>
+      <c r="B4099" s="17">
+        <v>654444</v>
+      </c>
+    </row>
+    <row r="4100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4100" t="s">
+        <v>318</v>
+      </c>
+      <c r="B4100" s="17">
+        <v>16845755</v>
+      </c>
+    </row>
+    <row r="4101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4101" s="18">
+        <v>44937</v>
+      </c>
+      <c r="B4101" s="17">
+        <v>615918</v>
+      </c>
+    </row>
+    <row r="4102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4102" s="18">
+        <v>44968</v>
+      </c>
+      <c r="B4102" s="17">
+        <v>624326</v>
+      </c>
+    </row>
+    <row r="4103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4103" s="18">
+        <v>44996</v>
+      </c>
+      <c r="B4103" s="17">
+        <v>690547</v>
+      </c>
+    </row>
+    <row r="4104" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4104" s="18">
+        <v>45027</v>
+      </c>
+      <c r="B4104" s="17">
+        <v>460090</v>
+      </c>
+    </row>
+    <row r="4105" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4105" s="18">
+        <v>45057</v>
+      </c>
+      <c r="B4105" s="17">
+        <v>319818</v>
+      </c>
+    </row>
+    <row r="4106" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4106" s="18">
+        <v>45088</v>
+      </c>
+      <c r="B4106" s="17">
+        <v>559997</v>
+      </c>
+    </row>
+    <row r="4107" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4107" s="18">
+        <v>45118</v>
+      </c>
+      <c r="B4107" s="17">
+        <v>593027</v>
+      </c>
+    </row>
+    <row r="4108" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4108" s="18">
+        <v>45149</v>
+      </c>
+      <c r="B4108" s="17">
+        <v>611609</v>
+      </c>
+    </row>
+    <row r="4109" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4109" s="18">
+        <v>45180</v>
+      </c>
+      <c r="B4109" s="17">
+        <v>632890</v>
+      </c>
+    </row>
+    <row r="4110" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4110" s="18">
+        <v>45210</v>
+      </c>
+      <c r="B4110" s="17">
+        <v>665228</v>
+      </c>
+    </row>
+    <row r="4111" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4111" s="18">
+        <v>45241</v>
+      </c>
+      <c r="B4111" s="17">
+        <v>442882</v>
+      </c>
+    </row>
+    <row r="4112" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4112" s="18">
+        <v>45271</v>
+      </c>
+      <c r="B4112" s="17">
+        <v>315513</v>
+      </c>
+    </row>
+    <row r="4113" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4113" t="s">
+        <v>3861</v>
+      </c>
+      <c r="B4113" s="17">
+        <v>562086</v>
+      </c>
+    </row>
+    <row r="4114" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4114" t="s">
+        <v>3862</v>
+      </c>
+      <c r="B4114" s="17">
+        <v>637423</v>
+      </c>
+    </row>
+    <row r="4115" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4115" t="s">
+        <v>3863</v>
+      </c>
+      <c r="B4115" s="17">
+        <v>600043</v>
+      </c>
+    </row>
+    <row r="4116" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4116" t="s">
+        <v>3864</v>
+      </c>
+      <c r="B4116" s="17">
+        <v>652891</v>
+      </c>
+    </row>
+    <row r="4117" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4117" t="s">
+        <v>3865</v>
+      </c>
+      <c r="B4117" s="17">
+        <v>688978</v>
+      </c>
+    </row>
+    <row r="4118" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4118" t="s">
+        <v>3866</v>
+      </c>
+      <c r="B4118" s="17">
+        <v>466724</v>
+      </c>
+    </row>
+    <row r="4119" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4119" t="s">
+        <v>3867</v>
+      </c>
+      <c r="B4119" s="17">
+        <v>308168</v>
+      </c>
+    </row>
+    <row r="4120" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4120" t="s">
+        <v>3868</v>
+      </c>
+      <c r="B4120" s="17">
+        <v>560403</v>
+      </c>
+    </row>
+    <row r="4121" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4121" t="s">
+        <v>3869</v>
+      </c>
+      <c r="B4121" s="17">
+        <v>588403</v>
+      </c>
+    </row>
+    <row r="4122" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4122" t="s">
+        <v>3870</v>
+      </c>
+      <c r="B4122" s="17">
+        <v>602305</v>
+      </c>
+    </row>
+    <row r="4123" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4123" t="s">
+        <v>3871</v>
+      </c>
+      <c r="B4123" s="17">
+        <v>654080</v>
+      </c>
+    </row>
+    <row r="4124" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4124" t="s">
+        <v>3872</v>
+      </c>
+      <c r="B4124" s="17">
+        <v>709400</v>
+      </c>
+    </row>
+    <row r="4125" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4125" t="s">
+        <v>3873</v>
+      </c>
+      <c r="B4125" s="17">
+        <v>461954</v>
+      </c>
+    </row>
+    <row r="4126" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4126" t="s">
+        <v>3874</v>
+      </c>
+      <c r="B4126" s="17">
+        <v>326749</v>
+      </c>
+    </row>
+    <row r="4127" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4127" t="s">
+        <v>3875</v>
+      </c>
+      <c r="B4127" s="17">
+        <v>570436</v>
+      </c>
+    </row>
+    <row r="4128" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4128" t="s">
+        <v>3876</v>
+      </c>
+      <c r="B4128" s="17">
+        <v>608405</v>
+      </c>
+    </row>
+    <row r="4129" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4129" t="s">
+        <v>3877</v>
+      </c>
+      <c r="B4129" s="17">
+        <v>631250</v>
+      </c>
+    </row>
+    <row r="4130" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4130" t="s">
+        <v>3878</v>
+      </c>
+      <c r="B4130" s="17">
+        <v>684212</v>
+      </c>
+    </row>
+    <row r="4131" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4131" t="s">
+        <v>349</v>
+      </c>
+      <c r="B4131" s="17">
+        <v>15103771</v>
+      </c>
+    </row>
+    <row r="4132" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4132" s="18">
+        <v>44938</v>
+      </c>
+      <c r="B4132" s="17">
+        <v>739145</v>
+      </c>
+    </row>
+    <row r="4133" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4133" s="18">
+        <v>44969</v>
+      </c>
+      <c r="B4133" s="17">
+        <v>506869</v>
+      </c>
+    </row>
+    <row r="4134" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4134" s="18">
+        <v>44997</v>
+      </c>
+      <c r="B4134" s="17">
+        <v>359302</v>
+      </c>
+    </row>
+    <row r="4135" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4135" s="18">
+        <v>45028</v>
+      </c>
+      <c r="B4135" s="17">
+        <v>613833</v>
+      </c>
+    </row>
+    <row r="4136" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4136" s="18">
+        <v>45058</v>
+      </c>
+      <c r="B4136" s="17">
+        <v>631871</v>
+      </c>
+    </row>
+    <row r="4137" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4137" s="18">
+        <v>45089</v>
+      </c>
+      <c r="B4137" s="17">
+        <v>658262</v>
+      </c>
+    </row>
+    <row r="4138" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4138" s="18">
+        <v>45119</v>
+      </c>
+      <c r="B4138" s="17">
+        <v>657774</v>
+      </c>
+    </row>
+    <row r="4139" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4139" s="18">
+        <v>45150</v>
+      </c>
+      <c r="B4139" s="17">
+        <v>710359</v>
+      </c>
+    </row>
+    <row r="4140" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4140" s="18">
+        <v>45181</v>
+      </c>
+      <c r="B4140" s="17">
+        <v>489356</v>
+      </c>
+    </row>
+    <row r="4141" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4141" s="18">
+        <v>45211</v>
+      </c>
+      <c r="B4141" s="17">
+        <v>345603</v>
+      </c>
+    </row>
+    <row r="4142" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4142" s="18">
+        <v>45242</v>
+      </c>
+      <c r="B4142" s="17">
+        <v>599273</v>
+      </c>
+    </row>
+    <row r="4143" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4143" s="18">
+        <v>45272</v>
+      </c>
+      <c r="B4143" s="17">
+        <v>629144</v>
+      </c>
+    </row>
+    <row r="4144" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4144" t="s">
+        <v>3879</v>
+      </c>
+      <c r="B4144" s="17">
+        <v>640685</v>
+      </c>
+    </row>
+    <row r="4145" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4145" t="s">
+        <v>3880</v>
+      </c>
+      <c r="B4145" s="17">
+        <v>643245</v>
+      </c>
+    </row>
+    <row r="4146" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4146" t="s">
+        <v>3881</v>
+      </c>
+      <c r="B4146" s="17">
+        <v>685044</v>
+      </c>
+    </row>
+    <row r="4147" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4147" t="s">
+        <v>3882</v>
+      </c>
+      <c r="B4147" s="17">
+        <v>475534</v>
+      </c>
+    </row>
+    <row r="4148" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4148" t="s">
+        <v>3883</v>
+      </c>
+      <c r="B4148" s="17">
+        <v>337481</v>
+      </c>
+    </row>
+    <row r="4149" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4149" t="s">
+        <v>3884</v>
+      </c>
+      <c r="B4149" s="17">
+        <v>587116</v>
+      </c>
+    </row>
+    <row r="4150" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4150" t="s">
+        <v>3885</v>
+      </c>
+      <c r="B4150" s="17">
+        <v>614224</v>
+      </c>
+    </row>
+    <row r="4151" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4151" t="s">
+        <v>3886</v>
+      </c>
+      <c r="B4151" s="17">
+        <v>606008</v>
+      </c>
+    </row>
+    <row r="4152" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4152" t="s">
+        <v>3887</v>
+      </c>
+      <c r="B4152" s="17">
+        <v>528845</v>
+      </c>
+    </row>
+    <row r="4153" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4153" t="s">
+        <v>3888</v>
+      </c>
+      <c r="B4153" s="17">
+        <v>477233</v>
+      </c>
+    </row>
+    <row r="4154" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4154" t="s">
+        <v>3889</v>
+      </c>
+      <c r="B4154" s="17">
+        <v>292725</v>
+      </c>
+    </row>
+    <row r="4155" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4155" t="s">
+        <v>3890</v>
+      </c>
+      <c r="B4155" s="17">
+        <v>145526</v>
+      </c>
+    </row>
+    <row r="4156" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4156" t="s">
+        <v>3891</v>
+      </c>
+      <c r="B4156" s="17">
+        <v>157714</v>
+      </c>
+    </row>
+    <row r="4157" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4157" t="s">
+        <v>3892</v>
+      </c>
+      <c r="B4157" s="17">
+        <v>205139</v>
+      </c>
+    </row>
+    <row r="4158" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4158" t="s">
+        <v>3893</v>
+      </c>
+      <c r="B4158" s="17">
+        <v>361520</v>
+      </c>
+    </row>
+    <row r="4159" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4159" t="s">
+        <v>3894</v>
+      </c>
+      <c r="B4159" s="17">
+        <v>373478</v>
+      </c>
+    </row>
+    <row r="4160" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4160" t="s">
+        <v>3895</v>
+      </c>
+      <c r="B4160" s="17">
+        <v>422671</v>
+      </c>
+    </row>
+    <row r="4161" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4161" t="s">
+        <v>3896</v>
+      </c>
+      <c r="B4161" s="17">
+        <v>335374</v>
+      </c>
+    </row>
+    <row r="4162" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4162" t="s">
+        <v>3897</v>
+      </c>
+      <c r="B4162" s="17">
+        <v>273418</v>
+      </c>
+    </row>
+    <row r="4163" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4163">
+        <v>2024</v>
+      </c>
+      <c r="B4163" s="17">
+        <v>165024700</v>
+      </c>
+    </row>
+    <row r="4164" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4164" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4164" s="17">
+        <v>16249214</v>
+      </c>
+    </row>
+    <row r="4165" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4165" s="18">
+        <v>45292</v>
+      </c>
+      <c r="B4165" s="17">
+        <v>239739</v>
+      </c>
+    </row>
+    <row r="4166" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4166" s="18">
+        <v>45323</v>
+      </c>
+      <c r="B4166" s="17">
+        <v>403500</v>
+      </c>
+    </row>
+    <row r="4167" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4167" s="18">
+        <v>45352</v>
+      </c>
+      <c r="B4167" s="17">
+        <v>412151</v>
+      </c>
+    </row>
+    <row r="4168" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4168" s="18">
+        <v>45383</v>
+      </c>
+      <c r="B4168" s="17">
+        <v>504834</v>
+      </c>
+    </row>
+    <row r="4169" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4169" s="18">
+        <v>45413</v>
+      </c>
+      <c r="B4169" s="17">
+        <v>604338</v>
+      </c>
+    </row>
+    <row r="4170" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4170" s="18">
+        <v>45444</v>
+      </c>
+      <c r="B4170" s="17">
+        <v>376211</v>
+      </c>
+    </row>
+    <row r="4171" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4171" s="18">
+        <v>45474</v>
+      </c>
+      <c r="B4171" s="17">
+        <v>276277</v>
+      </c>
+    </row>
+    <row r="4172" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4172" s="18">
+        <v>45505</v>
+      </c>
+      <c r="B4172" s="17">
+        <v>611928</v>
+      </c>
+    </row>
+    <row r="4173" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4173" s="18">
+        <v>45536</v>
+      </c>
+      <c r="B4173" s="17">
+        <v>638872</v>
+      </c>
+    </row>
+    <row r="4174" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4174" s="18">
+        <v>45566</v>
+      </c>
+      <c r="B4174" s="17">
+        <v>636759</v>
+      </c>
+    </row>
+    <row r="4175" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4175" s="18">
+        <v>45597</v>
+      </c>
+      <c r="B4175" s="17">
+        <v>640428</v>
+      </c>
+    </row>
+    <row r="4176" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4176" s="18">
+        <v>45627</v>
+      </c>
+      <c r="B4176" s="17">
+        <v>672711</v>
+      </c>
+    </row>
+    <row r="4177" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4177" t="s">
+        <v>3898</v>
+      </c>
+      <c r="B4177" s="17">
+        <v>405934</v>
+      </c>
+    </row>
+    <row r="4178" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4178" t="s">
+        <v>3899</v>
+      </c>
+      <c r="B4178" s="17">
+        <v>407804</v>
+      </c>
+    </row>
+    <row r="4179" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4179" t="s">
+        <v>3900</v>
+      </c>
+      <c r="B4179" s="17">
+        <v>627355</v>
+      </c>
+    </row>
+    <row r="4180" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4180" t="s">
+        <v>3901</v>
+      </c>
+      <c r="B4180" s="17">
+        <v>649882</v>
+      </c>
+    </row>
+    <row r="4181" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4181" t="s">
+        <v>3902</v>
+      </c>
+      <c r="B4181" s="17">
+        <v>642563</v>
+      </c>
+    </row>
+    <row r="4182" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4182" t="s">
+        <v>3903</v>
+      </c>
+      <c r="B4182" s="17">
+        <v>673195</v>
+      </c>
+    </row>
+    <row r="4183" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4183" t="s">
+        <v>3904</v>
+      </c>
+      <c r="B4183" s="17">
+        <v>686549</v>
+      </c>
+    </row>
+    <row r="4184" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4184" t="s">
+        <v>3905</v>
+      </c>
+      <c r="B4184" s="17">
+        <v>413510</v>
+      </c>
+    </row>
+    <row r="4185" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4185" t="s">
+        <v>3906</v>
+      </c>
+      <c r="B4185" s="17">
+        <v>286710</v>
+      </c>
+    </row>
+    <row r="4186" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4186" t="s">
+        <v>3907</v>
+      </c>
+      <c r="B4186" s="17">
+        <v>587242</v>
+      </c>
+    </row>
+    <row r="4187" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4187" t="s">
+        <v>3908</v>
+      </c>
+      <c r="B4187" s="17">
+        <v>591811</v>
+      </c>
+    </row>
+    <row r="4188" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4188" t="s">
+        <v>3909</v>
+      </c>
+      <c r="B4188" s="17">
+        <v>606396</v>
+      </c>
+    </row>
+    <row r="4189" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4189" t="s">
+        <v>3910</v>
+      </c>
+      <c r="B4189" s="17">
+        <v>615046</v>
+      </c>
+    </row>
+    <row r="4190" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4190" t="s">
+        <v>3911</v>
+      </c>
+      <c r="B4190" s="17">
+        <v>632627</v>
+      </c>
+    </row>
+    <row r="4191" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4191" t="s">
+        <v>3912</v>
+      </c>
+      <c r="B4191" s="17">
+        <v>408851</v>
+      </c>
+    </row>
+    <row r="4192" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4192" t="s">
+        <v>3913</v>
+      </c>
+      <c r="B4192" s="17">
+        <v>278603</v>
+      </c>
+    </row>
+    <row r="4193" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4193" t="s">
+        <v>3914</v>
+      </c>
+      <c r="B4193" s="17">
+        <v>544602</v>
+      </c>
+    </row>
+    <row r="4194" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4194" t="s">
+        <v>3915</v>
+      </c>
+      <c r="B4194" s="17">
+        <v>568682</v>
+      </c>
+    </row>
+    <row r="4195" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4195" t="s">
+        <v>3916</v>
+      </c>
+      <c r="B4195" s="17">
+        <v>604104</v>
+      </c>
+    </row>
+    <row r="4196" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4196" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4196" s="17">
+        <v>14495019</v>
+      </c>
+    </row>
+    <row r="4197" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4197" s="18">
+        <v>45293</v>
+      </c>
+      <c r="B4197" s="17">
+        <v>627946</v>
+      </c>
+    </row>
+    <row r="4198" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4198" s="18">
+        <v>45324</v>
+      </c>
+      <c r="B4198" s="17">
+        <v>658134</v>
+      </c>
+    </row>
+    <row r="4199" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4199" s="18">
+        <v>45353</v>
+      </c>
+      <c r="B4199" s="17">
+        <v>432372</v>
+      </c>
+    </row>
+    <row r="4200" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4200" s="18">
+        <v>45384</v>
+      </c>
+      <c r="B4200" s="17">
+        <v>285884</v>
+      </c>
+    </row>
+    <row r="4201" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4201" s="18">
+        <v>45414</v>
+      </c>
+      <c r="B4201" s="17">
+        <v>583308</v>
+      </c>
+    </row>
+    <row r="4202" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4202" s="18">
+        <v>45445</v>
+      </c>
+      <c r="B4202" s="17">
+        <v>636224</v>
+      </c>
+    </row>
+    <row r="4203" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4203" s="18">
+        <v>45475</v>
+      </c>
+      <c r="B4203" s="17">
+        <v>609703</v>
+      </c>
+    </row>
+    <row r="4204" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4204" s="18">
+        <v>45506</v>
+      </c>
+      <c r="B4204" s="17">
+        <v>624417</v>
+      </c>
+    </row>
+    <row r="4205" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4205" s="18">
+        <v>45537</v>
+      </c>
+      <c r="B4205" s="17">
+        <v>645203</v>
+      </c>
+    </row>
+    <row r="4206" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4206" s="18">
+        <v>45567</v>
+      </c>
+      <c r="B4206" s="17">
+        <v>376014</v>
+      </c>
+    </row>
+    <row r="4207" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4207" s="18">
+        <v>45598</v>
+      </c>
+      <c r="B4207" s="17">
+        <v>260715</v>
+      </c>
+    </row>
+    <row r="4208" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4208" s="18">
+        <v>45628</v>
+      </c>
+      <c r="B4208" s="17">
+        <v>461420</v>
+      </c>
+    </row>
+    <row r="4209" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4209" t="s">
+        <v>3917</v>
+      </c>
+      <c r="B4209" s="17">
+        <v>491512</v>
+      </c>
+    </row>
+    <row r="4210" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4210" t="s">
+        <v>3918</v>
+      </c>
+      <c r="B4210" s="17">
+        <v>487681</v>
+      </c>
+    </row>
+    <row r="4211" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4211" t="s">
+        <v>3919</v>
+      </c>
+      <c r="B4211" s="17">
+        <v>481729</v>
+      </c>
+    </row>
+    <row r="4212" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4212" t="s">
+        <v>3920</v>
+      </c>
+      <c r="B4212" s="17">
+        <v>496819</v>
+      </c>
+    </row>
+    <row r="4213" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4213" t="s">
+        <v>3921</v>
+      </c>
+      <c r="B4213" s="17">
+        <v>377247</v>
+      </c>
+    </row>
+    <row r="4214" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4214" t="s">
+        <v>3922</v>
+      </c>
+      <c r="B4214" s="17">
+        <v>256699</v>
+      </c>
+    </row>
+    <row r="4215" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4215" t="s">
+        <v>3923</v>
+      </c>
+      <c r="B4215" s="17">
+        <v>512317</v>
+      </c>
+    </row>
+    <row r="4216" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4216" t="s">
+        <v>3924</v>
+      </c>
+      <c r="B4216" s="17">
+        <v>537391</v>
+      </c>
+    </row>
+    <row r="4217" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4217" t="s">
+        <v>3925</v>
+      </c>
+      <c r="B4217" s="17">
+        <v>543164</v>
+      </c>
+    </row>
+    <row r="4218" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4218" t="s">
+        <v>3926</v>
+      </c>
+      <c r="B4218" s="17">
+        <v>549905</v>
+      </c>
+    </row>
+    <row r="4219" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4219" t="s">
+        <v>3927</v>
+      </c>
+      <c r="B4219" s="17">
+        <v>590642</v>
+      </c>
+    </row>
+    <row r="4220" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4220" t="s">
+        <v>3928</v>
+      </c>
+      <c r="B4220" s="17">
+        <v>385179</v>
+      </c>
+    </row>
+    <row r="4221" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4221" t="s">
+        <v>3929</v>
+      </c>
+      <c r="B4221" s="17">
+        <v>270016</v>
+      </c>
+    </row>
+    <row r="4222" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4222" t="s">
+        <v>3930</v>
+      </c>
+      <c r="B4222" s="17">
+        <v>549077</v>
+      </c>
+    </row>
+    <row r="4223" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4223" t="s">
+        <v>3931</v>
+      </c>
+      <c r="B4223" s="17">
+        <v>570753</v>
+      </c>
+    </row>
+    <row r="4224" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4224" t="s">
+        <v>3932</v>
+      </c>
+      <c r="B4224" s="17">
+        <v>578121</v>
+      </c>
+    </row>
+    <row r="4225" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4225" t="s">
+        <v>3933</v>
+      </c>
+      <c r="B4225" s="17">
+        <v>615427</v>
+      </c>
+    </row>
+    <row r="4226" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4226" t="s">
+        <v>65</v>
+      </c>
+      <c r="B4226" s="17">
+        <v>14758133</v>
+      </c>
+    </row>
+    <row r="4227" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4227" s="18">
+        <v>45294</v>
+      </c>
+      <c r="B4227" s="17">
+        <v>651740</v>
+      </c>
+    </row>
+    <row r="4228" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4228" s="18">
+        <v>45325</v>
+      </c>
+      <c r="B4228" s="17">
+        <v>426861</v>
+      </c>
+    </row>
+    <row r="4229" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4229" s="18">
+        <v>45354</v>
+      </c>
+      <c r="B4229" s="17">
+        <v>307671</v>
+      </c>
+    </row>
+    <row r="4230" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4230" s="18">
+        <v>45385</v>
+      </c>
+      <c r="B4230" s="17">
+        <v>554793</v>
+      </c>
+    </row>
+    <row r="4231" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4231" s="18">
+        <v>45415</v>
+      </c>
+      <c r="B4231" s="17">
+        <v>579952</v>
+      </c>
+    </row>
+    <row r="4232" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4232" s="18">
+        <v>45446</v>
+      </c>
+      <c r="B4232" s="17">
+        <v>589258</v>
+      </c>
+    </row>
+    <row r="4233" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4233" s="18">
+        <v>45476</v>
+      </c>
+      <c r="B4233" s="17">
+        <v>601299</v>
+      </c>
+    </row>
+    <row r="4234" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4234" s="18">
+        <v>45507</v>
+      </c>
+      <c r="B4234" s="17">
+        <v>636649</v>
+      </c>
+    </row>
+    <row r="4235" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4235" s="18">
+        <v>45538</v>
+      </c>
+      <c r="B4235" s="17">
+        <v>422814</v>
+      </c>
+    </row>
+    <row r="4236" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4236" s="18">
+        <v>45568</v>
+      </c>
+      <c r="B4236" s="17">
+        <v>309021</v>
+      </c>
+    </row>
+    <row r="4237" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4237" s="18">
+        <v>45599</v>
+      </c>
+      <c r="B4237" s="17">
+        <v>552617</v>
+      </c>
+    </row>
+    <row r="4238" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4238" s="18">
+        <v>45629</v>
+      </c>
+      <c r="B4238" s="17">
+        <v>578328</v>
+      </c>
+    </row>
+    <row r="4239" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4239" t="s">
+        <v>3934</v>
+      </c>
+      <c r="B4239" s="17">
+        <v>577472</v>
+      </c>
+    </row>
+    <row r="4240" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4240" t="s">
+        <v>3935</v>
+      </c>
+      <c r="B4240" s="17">
+        <v>589742</v>
+      </c>
+    </row>
+    <row r="4241" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4241" t="s">
+        <v>3936</v>
+      </c>
+      <c r="B4241" s="17">
+        <v>629284</v>
+      </c>
+    </row>
+    <row r="4242" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4242" t="s">
+        <v>3937</v>
+      </c>
+      <c r="B4242" s="17">
+        <v>423485</v>
+      </c>
+    </row>
+    <row r="4243" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4243" t="s">
+        <v>3938</v>
+      </c>
+      <c r="B4243" s="17">
+        <v>298404</v>
+      </c>
+    </row>
+    <row r="4244" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4244" t="s">
+        <v>3939</v>
+      </c>
+      <c r="B4244" s="17">
+        <v>543131</v>
+      </c>
+    </row>
+    <row r="4245" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4245" t="s">
+        <v>3940</v>
+      </c>
+      <c r="B4245" s="17">
+        <v>574329</v>
+      </c>
+    </row>
+    <row r="4246" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4246" t="s">
+        <v>3941</v>
+      </c>
+      <c r="B4246" s="17">
+        <v>577066</v>
+      </c>
+    </row>
+    <row r="4247" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4247" t="s">
+        <v>3942</v>
+      </c>
+      <c r="B4247" s="17">
+        <v>598563</v>
+      </c>
+    </row>
+    <row r="4248" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4248" t="s">
+        <v>3943</v>
+      </c>
+      <c r="B4248" s="17">
+        <v>617406</v>
+      </c>
+    </row>
+    <row r="4249" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4249" t="s">
+        <v>3944</v>
+      </c>
+      <c r="B4249" s="17">
+        <v>403480</v>
+      </c>
+    </row>
+    <row r="4250" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4250" t="s">
+        <v>3945</v>
+      </c>
+      <c r="B4250" s="17">
+        <v>271450</v>
+      </c>
+    </row>
+    <row r="4251" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4251" t="s">
+        <v>3946</v>
+      </c>
+      <c r="B4251" s="17">
+        <v>403112</v>
+      </c>
+    </row>
+    <row r="4252" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4252" t="s">
+        <v>3947</v>
+      </c>
+      <c r="B4252" s="17">
+        <v>419879</v>
+      </c>
+    </row>
+    <row r="4253" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4253" t="s">
+        <v>3948</v>
+      </c>
+      <c r="B4253" s="17">
+        <v>448048</v>
+      </c>
+    </row>
+    <row r="4254" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4254" t="s">
+        <v>3949</v>
+      </c>
+      <c r="B4254" s="17">
+        <v>276296</v>
+      </c>
+    </row>
+    <row r="4255" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4255" t="s">
+        <v>3950</v>
+      </c>
+      <c r="B4255" s="17">
+        <v>279953</v>
+      </c>
+    </row>
+    <row r="4256" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4256" t="s">
+        <v>3951</v>
+      </c>
+      <c r="B4256" s="17">
+        <v>352236</v>
+      </c>
+    </row>
+    <row r="4257" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4257" t="s">
+        <v>3952</v>
+      </c>
+      <c r="B4257" s="17">
+        <v>263794</v>
+      </c>
+    </row>
+    <row r="4258" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4258" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4258" s="17">
+        <v>15240930</v>
+      </c>
+    </row>
+    <row r="4259" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4259" s="18">
+        <v>45295</v>
+      </c>
+      <c r="B4259" s="17">
+        <v>241048</v>
+      </c>
+    </row>
+    <row r="4260" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4260" s="18">
+        <v>45326</v>
+      </c>
+      <c r="B4260" s="17">
+        <v>590449</v>
+      </c>
+    </row>
+    <row r="4261" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4261" s="18">
+        <v>45355</v>
+      </c>
+      <c r="B4261" s="17">
+        <v>572630</v>
+      </c>
+    </row>
+    <row r="4262" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4262" s="18">
+        <v>45386</v>
+      </c>
+      <c r="B4262" s="17">
+        <v>618188</v>
+      </c>
+    </row>
+    <row r="4263" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4263" s="18">
+        <v>45416</v>
+      </c>
+      <c r="B4263" s="17">
+        <v>631149</v>
+      </c>
+    </row>
+    <row r="4264" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4264" s="18">
+        <v>45447</v>
+      </c>
+      <c r="B4264" s="17">
+        <v>370187</v>
+      </c>
+    </row>
+    <row r="4265" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4265" s="18">
+        <v>45477</v>
+      </c>
+      <c r="B4265" s="17">
+        <v>285404</v>
+      </c>
+    </row>
+    <row r="4266" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4266" s="18">
+        <v>45508</v>
+      </c>
+      <c r="B4266" s="17">
+        <v>540864</v>
+      </c>
+    </row>
+    <row r="4267" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4267" s="18">
+        <v>45539</v>
+      </c>
+      <c r="B4267" s="17">
+        <v>560583</v>
+      </c>
+    </row>
+    <row r="4268" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4268" s="18">
+        <v>45569</v>
+      </c>
+      <c r="B4268" s="17">
+        <v>579636</v>
+      </c>
+    </row>
+    <row r="4269" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4269" s="18">
+        <v>45600</v>
+      </c>
+      <c r="B4269" s="17">
+        <v>605647</v>
+      </c>
+    </row>
+    <row r="4270" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4270" s="18">
+        <v>45630</v>
+      </c>
+      <c r="B4270" s="17">
+        <v>634985</v>
+      </c>
+    </row>
+    <row r="4271" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4271" t="s">
+        <v>3953</v>
+      </c>
+      <c r="B4271" s="17">
+        <v>428975</v>
+      </c>
+    </row>
+    <row r="4272" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4272" t="s">
+        <v>3954</v>
+      </c>
+      <c r="B4272" s="17">
+        <v>302942</v>
+      </c>
+    </row>
+    <row r="4273" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4273" t="s">
+        <v>3955</v>
+      </c>
+      <c r="B4273" s="17">
+        <v>536939</v>
+      </c>
+    </row>
+    <row r="4274" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4274" t="s">
+        <v>3956</v>
+      </c>
+      <c r="B4274" s="17">
+        <v>569168</v>
+      </c>
+    </row>
+    <row r="4275" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4275" t="s">
+        <v>3957</v>
+      </c>
+      <c r="B4275" s="17">
+        <v>572837</v>
+      </c>
+    </row>
+    <row r="4276" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4276" t="s">
+        <v>3958</v>
+      </c>
+      <c r="B4276" s="17">
+        <v>583340</v>
+      </c>
+    </row>
+    <row r="4277" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4277" t="s">
+        <v>3959</v>
+      </c>
+      <c r="B4277" s="17">
+        <v>646005</v>
+      </c>
+    </row>
+    <row r="4278" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4278" t="s">
+        <v>3960</v>
+      </c>
+      <c r="B4278" s="17">
+        <v>431170</v>
+      </c>
+    </row>
+    <row r="4279" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4279" t="s">
+        <v>3961</v>
+      </c>
+      <c r="B4279" s="17">
+        <v>312178</v>
+      </c>
+    </row>
+    <row r="4280" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4280" t="s">
+        <v>3962</v>
+      </c>
+      <c r="B4280" s="17">
+        <v>529108</v>
+      </c>
+    </row>
+    <row r="4281" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4281" t="s">
+        <v>3963</v>
+      </c>
+      <c r="B4281" s="17">
+        <v>565520</v>
+      </c>
+    </row>
+    <row r="4282" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4282" t="s">
+        <v>3964</v>
+      </c>
+      <c r="B4282" s="17">
+        <v>567051</v>
+      </c>
+    </row>
+    <row r="4283" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4283" t="s">
+        <v>3965</v>
+      </c>
+      <c r="B4283" s="17">
+        <v>581642</v>
+      </c>
+    </row>
+    <row r="4284" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4284" t="s">
+        <v>3966</v>
+      </c>
+      <c r="B4284" s="17">
+        <v>596905</v>
+      </c>
+    </row>
+    <row r="4285" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4285" t="s">
+        <v>3967</v>
+      </c>
+      <c r="B4285" s="17">
+        <v>401705</v>
+      </c>
+    </row>
+    <row r="4286" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4286" t="s">
+        <v>3968</v>
+      </c>
+      <c r="B4286" s="17">
+        <v>306086</v>
+      </c>
+    </row>
+    <row r="4287" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4287" t="s">
+        <v>3969</v>
+      </c>
+      <c r="B4287" s="17">
+        <v>516124</v>
+      </c>
+    </row>
+    <row r="4288" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4288" t="s">
+        <v>3970</v>
+      </c>
+      <c r="B4288" s="17">
+        <v>562465</v>
+      </c>
+    </row>
+    <row r="4289" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4289" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4289" s="17">
+        <v>14839425</v>
+      </c>
+    </row>
+    <row r="4290" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4290" s="18">
+        <v>45296</v>
+      </c>
+      <c r="B4290" s="17">
+        <v>559190</v>
+      </c>
+    </row>
+    <row r="4291" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4291" s="18">
+        <v>45327</v>
+      </c>
+      <c r="B4291" s="17">
+        <v>584818</v>
+      </c>
+    </row>
+    <row r="4292" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4292" s="18">
+        <v>45356</v>
+      </c>
+      <c r="B4292" s="17">
+        <v>616808</v>
+      </c>
+    </row>
+    <row r="4293" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4293" s="18">
+        <v>45387</v>
+      </c>
+      <c r="B4293" s="17">
+        <v>422938</v>
+      </c>
+    </row>
+    <row r="4294" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4294" s="18">
+        <v>45417</v>
+      </c>
+      <c r="B4294" s="17">
+        <v>328309</v>
+      </c>
+    </row>
+    <row r="4295" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4295" s="18">
+        <v>45448</v>
+      </c>
+      <c r="B4295" s="17">
+        <v>528320</v>
+      </c>
+    </row>
+    <row r="4296" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4296" s="18">
+        <v>45478</v>
+      </c>
+      <c r="B4296" s="17">
+        <v>554395</v>
+      </c>
+    </row>
+    <row r="4297" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4297" s="18">
+        <v>45509</v>
+      </c>
+      <c r="B4297" s="17">
+        <v>593907</v>
+      </c>
+    </row>
+    <row r="4298" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4298" s="18">
+        <v>45540</v>
+      </c>
+      <c r="B4298" s="17">
+        <v>310930</v>
+      </c>
+    </row>
+    <row r="4299" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4299" s="18">
+        <v>45570</v>
+      </c>
+      <c r="B4299" s="17">
+        <v>441188</v>
+      </c>
+    </row>
+    <row r="4300" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4300" s="18">
+        <v>45601</v>
+      </c>
+      <c r="B4300" s="17">
+        <v>382437</v>
+      </c>
+    </row>
+    <row r="4301" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4301" s="18">
+        <v>45631</v>
+      </c>
+      <c r="B4301" s="17">
+        <v>287239</v>
+      </c>
+    </row>
+    <row r="4302" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4302" t="s">
+        <v>3971</v>
+      </c>
+      <c r="B4302" s="17">
+        <v>512481</v>
+      </c>
+    </row>
+    <row r="4303" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4303" t="s">
+        <v>3972</v>
+      </c>
+      <c r="B4303" s="17">
+        <v>532061</v>
+      </c>
+    </row>
+    <row r="4304" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4304" t="s">
+        <v>3973</v>
+      </c>
+      <c r="B4304" s="17">
+        <v>543634</v>
+      </c>
+    </row>
+    <row r="4305" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4305" t="s">
+        <v>3974</v>
+      </c>
+      <c r="B4305" s="17">
+        <v>553401</v>
+      </c>
+    </row>
+    <row r="4306" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4306" t="s">
+        <v>3975</v>
+      </c>
+      <c r="B4306" s="17">
+        <v>589075</v>
+      </c>
+    </row>
+    <row r="4307" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4307" t="s">
+        <v>3976</v>
+      </c>
+      <c r="B4307" s="17">
+        <v>374354</v>
+      </c>
+    </row>
+    <row r="4308" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4308" t="s">
+        <v>3977</v>
+      </c>
+      <c r="B4308" s="17">
+        <v>282979</v>
+      </c>
+    </row>
+    <row r="4309" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4309" t="s">
+        <v>3978</v>
+      </c>
+      <c r="B4309" s="17">
+        <v>303369</v>
+      </c>
+    </row>
+    <row r="4310" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4310" t="s">
+        <v>3979</v>
+      </c>
+      <c r="B4310" s="17">
+        <v>525580</v>
+      </c>
+    </row>
+    <row r="4311" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4311" t="s">
+        <v>3980</v>
+      </c>
+      <c r="B4311" s="17">
+        <v>532078</v>
+      </c>
+    </row>
+    <row r="4312" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4312" t="s">
+        <v>3981</v>
+      </c>
+      <c r="B4312" s="17">
+        <v>546175</v>
+      </c>
+    </row>
+    <row r="4313" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4313" t="s">
+        <v>3982</v>
+      </c>
+      <c r="B4313" s="17">
+        <v>568984</v>
+      </c>
+    </row>
+    <row r="4314" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4314" t="s">
+        <v>3983</v>
+      </c>
+      <c r="B4314" s="17">
+        <v>389217</v>
+      </c>
+    </row>
+    <row r="4315" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4315" t="s">
+        <v>3984</v>
+      </c>
+      <c r="B4315" s="17">
+        <v>283711</v>
+      </c>
+    </row>
+    <row r="4316" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4316" t="s">
+        <v>3985</v>
+      </c>
+      <c r="B4316" s="17">
+        <v>486325</v>
+      </c>
+    </row>
+    <row r="4317" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4317" t="s">
+        <v>3986</v>
+      </c>
+      <c r="B4317" s="17">
+        <v>518994</v>
+      </c>
+    </row>
+    <row r="4318" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4318" t="s">
+        <v>3987</v>
+      </c>
+      <c r="B4318" s="17">
+        <v>522424</v>
+      </c>
+    </row>
+    <row r="4319" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4319" t="s">
+        <v>3988</v>
+      </c>
+      <c r="B4319" s="17">
+        <v>555229</v>
+      </c>
+    </row>
+    <row r="4320" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4320" t="s">
+        <v>3989</v>
+      </c>
+      <c r="B4320" s="17">
+        <v>608875</v>
+      </c>
+    </row>
+    <row r="4321" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4321" t="s">
+        <v>160</v>
+      </c>
+      <c r="B4321" s="17">
+        <v>14073542</v>
+      </c>
+    </row>
+    <row r="4322" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4322" s="18">
+        <v>45297</v>
+      </c>
+      <c r="B4322" s="17">
+        <v>418139</v>
+      </c>
+    </row>
+    <row r="4323" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4323" s="18">
+        <v>45328</v>
+      </c>
+      <c r="B4323" s="17">
+        <v>295186</v>
+      </c>
+    </row>
+    <row r="4324" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4324" s="18">
+        <v>45357</v>
+      </c>
+      <c r="B4324" s="17">
+        <v>498098</v>
+      </c>
+    </row>
+    <row r="4325" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4325" s="18">
+        <v>45388</v>
+      </c>
+      <c r="B4325" s="17">
+        <v>548337</v>
+      </c>
+    </row>
+    <row r="4326" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4326" s="18">
+        <v>45418</v>
+      </c>
+      <c r="B4326" s="17">
+        <v>355397</v>
+      </c>
+    </row>
+    <row r="4327" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4327" s="18">
+        <v>45449</v>
+      </c>
+      <c r="B4327" s="17">
+        <v>544232</v>
+      </c>
+    </row>
+    <row r="4328" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4328" s="18">
+        <v>45479</v>
+      </c>
+      <c r="B4328" s="17">
+        <v>584703</v>
+      </c>
+    </row>
+    <row r="4329" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4329" s="18">
+        <v>45510</v>
+      </c>
+      <c r="B4329" s="17">
+        <v>403853</v>
+      </c>
+    </row>
+    <row r="4330" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4330" s="18">
+        <v>45541</v>
+      </c>
+      <c r="B4330" s="17">
+        <v>288010</v>
+      </c>
+    </row>
+    <row r="4331" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4331" s="18">
+        <v>45571</v>
+      </c>
+      <c r="B4331" s="17">
+        <v>500244</v>
+      </c>
+    </row>
+    <row r="4332" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4332" s="18">
+        <v>45602</v>
+      </c>
+      <c r="B4332" s="17">
+        <v>543925</v>
+      </c>
+    </row>
+    <row r="4333" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4333" s="18">
+        <v>45632</v>
+      </c>
+      <c r="B4333" s="17">
+        <v>537056</v>
+      </c>
+    </row>
+    <row r="4334" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4334" t="s">
+        <v>3990</v>
+      </c>
+      <c r="B4334" s="17">
+        <v>540736</v>
+      </c>
+    </row>
+    <row r="4335" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4335" t="s">
+        <v>3991</v>
+      </c>
+      <c r="B4335" s="17">
+        <v>591926</v>
+      </c>
+    </row>
+    <row r="4336" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4336" t="s">
+        <v>3992</v>
+      </c>
+      <c r="B4336" s="17">
+        <v>368742</v>
+      </c>
+    </row>
+    <row r="4337" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4337" t="s">
+        <v>3993</v>
+      </c>
+      <c r="B4337" s="17">
+        <v>322797</v>
+      </c>
+    </row>
+    <row r="4338" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4338" t="s">
+        <v>3994</v>
+      </c>
+      <c r="B4338" s="17">
+        <v>486541</v>
+      </c>
+    </row>
+    <row r="4339" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4339" t="s">
+        <v>3995</v>
+      </c>
+      <c r="B4339" s="17">
+        <v>517465</v>
+      </c>
+    </row>
+    <row r="4340" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4340" t="s">
+        <v>3996</v>
+      </c>
+      <c r="B4340" s="17">
+        <v>524958</v>
+      </c>
+    </row>
+    <row r="4341" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4341" t="s">
+        <v>3997</v>
+      </c>
+      <c r="B4341" s="17">
+        <v>564078</v>
+      </c>
+    </row>
+    <row r="4342" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4342" t="s">
+        <v>3998</v>
+      </c>
+      <c r="B4342" s="17">
+        <v>606715</v>
+      </c>
+    </row>
+    <row r="4343" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4343" t="s">
+        <v>3999</v>
+      </c>
+      <c r="B4343" s="17">
+        <v>415768</v>
+      </c>
+    </row>
+    <row r="4344" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4344" t="s">
+        <v>4000</v>
+      </c>
+      <c r="B4344" s="17">
+        <v>335997</v>
+      </c>
+    </row>
+    <row r="4345" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4345" t="s">
+        <v>4001</v>
+      </c>
+      <c r="B4345" s="17">
+        <v>497246</v>
+      </c>
+    </row>
+    <row r="4346" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4346" t="s">
+        <v>4002</v>
+      </c>
+      <c r="B4346" s="17">
+        <v>546058</v>
+      </c>
+    </row>
+    <row r="4347" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4347" t="s">
+        <v>4003</v>
+      </c>
+      <c r="B4347" s="17">
+        <v>530715</v>
+      </c>
+    </row>
+    <row r="4348" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4348" t="s">
+        <v>4004</v>
+      </c>
+      <c r="B4348" s="17">
+        <v>530808</v>
+      </c>
+    </row>
+    <row r="4349" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4349" t="s">
+        <v>4005</v>
+      </c>
+      <c r="B4349" s="17">
+        <v>538305</v>
+      </c>
+    </row>
+    <row r="4350" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4350" t="s">
+        <v>4006</v>
+      </c>
+      <c r="B4350" s="17">
+        <v>391099</v>
+      </c>
+    </row>
+    <row r="4351" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4351" t="s">
+        <v>4007</v>
+      </c>
+      <c r="B4351" s="17">
+        <v>246408</v>
+      </c>
+    </row>
+    <row r="4352" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4352" t="s">
+        <v>191</v>
+      </c>
+      <c r="B4352" s="17">
+        <v>10465980</v>
+      </c>
+    </row>
+    <row r="4353" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4353" s="18">
+        <v>45298</v>
+      </c>
+      <c r="B4353" s="17">
+        <v>409564</v>
+      </c>
+    </row>
+    <row r="4354" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4354" s="18">
+        <v>45329</v>
+      </c>
+      <c r="B4354" s="17">
+        <v>426367</v>
+      </c>
+    </row>
+    <row r="4355" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4355" s="18">
+        <v>45358</v>
+      </c>
+      <c r="B4355" s="17">
+        <v>432434</v>
+      </c>
+    </row>
+    <row r="4356" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4356" s="18">
+        <v>45389</v>
+      </c>
+      <c r="B4356" s="17">
+        <v>423631</v>
+      </c>
+    </row>
+    <row r="4357" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4357" s="18">
+        <v>45419</v>
+      </c>
+      <c r="B4357" s="17">
+        <v>447861</v>
+      </c>
+    </row>
+    <row r="4358" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4358" s="18">
+        <v>45450</v>
+      </c>
+      <c r="B4358" s="17">
+        <v>354993</v>
+      </c>
+    </row>
+    <row r="4359" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4359" s="18">
+        <v>45480</v>
+      </c>
+      <c r="B4359" s="17">
+        <v>265643</v>
+      </c>
+    </row>
+    <row r="4360" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4360" s="18">
+        <v>45511</v>
+      </c>
+      <c r="B4360" s="17">
+        <v>367054</v>
+      </c>
+    </row>
+    <row r="4361" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4361" s="18">
+        <v>45542</v>
+      </c>
+      <c r="B4361" s="17">
+        <v>385662</v>
+      </c>
+    </row>
+    <row r="4362" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4362" s="18">
+        <v>45572</v>
+      </c>
+      <c r="B4362" s="17">
+        <v>363510</v>
+      </c>
+    </row>
+    <row r="4363" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4363" s="18">
+        <v>45603</v>
+      </c>
+      <c r="B4363" s="17">
+        <v>381508</v>
+      </c>
+    </row>
+    <row r="4364" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4364" s="18">
+        <v>45633</v>
+      </c>
+      <c r="B4364" s="17">
+        <v>386005</v>
+      </c>
+    </row>
+    <row r="4365" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4365" t="s">
+        <v>4008</v>
+      </c>
+      <c r="B4365" s="17">
+        <v>261793</v>
+      </c>
+    </row>
+    <row r="4366" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4366" t="s">
+        <v>4009</v>
+      </c>
+      <c r="B4366" s="17">
+        <v>238867</v>
+      </c>
+    </row>
+    <row r="4367" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4367" t="s">
+        <v>4010</v>
+      </c>
+      <c r="B4367" s="17">
+        <v>312725</v>
+      </c>
+    </row>
+    <row r="4368" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4368" t="s">
+        <v>4011</v>
+      </c>
+      <c r="B4368" s="17">
+        <v>313042</v>
+      </c>
+    </row>
+    <row r="4369" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4369" t="s">
+        <v>4012</v>
+      </c>
+      <c r="B4369" s="17">
+        <v>319413</v>
+      </c>
+    </row>
+    <row r="4370" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4370" t="s">
+        <v>4013</v>
+      </c>
+      <c r="B4370" s="17">
+        <v>338702</v>
+      </c>
+    </row>
+    <row r="4371" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4371" t="s">
+        <v>4014</v>
+      </c>
+      <c r="B4371" s="17">
+        <v>344687</v>
+      </c>
+    </row>
+    <row r="4372" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4372" t="s">
+        <v>4015</v>
+      </c>
+      <c r="B4372" s="17">
+        <v>298312</v>
+      </c>
+    </row>
+    <row r="4373" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4373" t="s">
+        <v>4016</v>
+      </c>
+      <c r="B4373" s="17">
+        <v>230204</v>
+      </c>
+    </row>
+    <row r="4374" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4374" t="s">
+        <v>4017</v>
+      </c>
+      <c r="B4374" s="17">
+        <v>286924</v>
+      </c>
+    </row>
+    <row r="4375" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4375" t="s">
+        <v>4018</v>
+      </c>
+      <c r="B4375" s="17">
+        <v>308948</v>
+      </c>
+    </row>
+    <row r="4376" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4376" t="s">
+        <v>4019</v>
+      </c>
+      <c r="B4376" s="17">
+        <v>325645</v>
+      </c>
+    </row>
+    <row r="4377" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4377" t="s">
+        <v>4020</v>
+      </c>
+      <c r="B4377" s="17">
+        <v>329223</v>
+      </c>
+    </row>
+    <row r="4378" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4378" t="s">
+        <v>4021</v>
+      </c>
+      <c r="B4378" s="17">
+        <v>334163</v>
+      </c>
+    </row>
+    <row r="4379" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4379" t="s">
+        <v>4022</v>
+      </c>
+      <c r="B4379" s="17">
+        <v>293297</v>
+      </c>
+    </row>
+    <row r="4380" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4380" t="s">
+        <v>4023</v>
+      </c>
+      <c r="B4380" s="17">
+        <v>252899</v>
+      </c>
+    </row>
+    <row r="4381" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4381" t="s">
+        <v>4024</v>
+      </c>
+      <c r="B4381" s="17">
+        <v>322655</v>
+      </c>
+    </row>
+    <row r="4382" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4382" t="s">
+        <v>4025</v>
+      </c>
+      <c r="B4382" s="17">
+        <v>341410</v>
+      </c>
+    </row>
+    <row r="4383" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4383" t="s">
+        <v>4026</v>
+      </c>
+      <c r="B4383" s="17">
+        <v>368839</v>
+      </c>
+    </row>
+    <row r="4384" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4384" t="s">
+        <v>223</v>
+      </c>
+      <c r="B4384" s="17">
+        <v>13517484</v>
+      </c>
+    </row>
+    <row r="4385" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4385" s="18">
+        <v>45299</v>
+      </c>
+      <c r="B4385" s="17">
+        <v>383776</v>
+      </c>
+    </row>
+    <row r="4386" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4386" s="18">
+        <v>45330</v>
+      </c>
+      <c r="B4386" s="17">
+        <v>402332</v>
+      </c>
+    </row>
+    <row r="4387" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4387" s="18">
+        <v>45359</v>
+      </c>
+      <c r="B4387" s="17">
+        <v>342604</v>
+      </c>
+    </row>
+    <row r="4388" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4388" s="18">
+        <v>45390</v>
+      </c>
+      <c r="B4388" s="17">
+        <v>248164</v>
+      </c>
+    </row>
+    <row r="4389" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4389" s="18">
+        <v>45420</v>
+      </c>
+      <c r="B4389" s="17">
+        <v>382627</v>
+      </c>
+    </row>
+    <row r="4390" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4390" s="18">
+        <v>45451</v>
+      </c>
+      <c r="B4390" s="17">
+        <v>414109</v>
+      </c>
+    </row>
+    <row r="4391" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4391" s="18">
+        <v>45481</v>
+      </c>
+      <c r="B4391" s="17">
+        <v>415847</v>
+      </c>
+    </row>
+    <row r="4392" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4392" s="18">
+        <v>45512</v>
+      </c>
+      <c r="B4392" s="17">
+        <v>434272</v>
+      </c>
+    </row>
+    <row r="4393" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4393" s="18">
+        <v>45543</v>
+      </c>
+      <c r="B4393" s="17">
+        <v>457998</v>
+      </c>
+    </row>
+    <row r="4394" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4394" s="18">
+        <v>45573</v>
+      </c>
+      <c r="B4394" s="17">
+        <v>370495</v>
+      </c>
+    </row>
+    <row r="4395" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4395" s="18">
+        <v>45604</v>
+      </c>
+      <c r="B4395" s="17">
+        <v>258590</v>
+      </c>
+    </row>
+    <row r="4396" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4396" s="18">
+        <v>45634</v>
+      </c>
+      <c r="B4396" s="17">
+        <v>448603</v>
+      </c>
+    </row>
+    <row r="4397" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4397" t="s">
+        <v>4027</v>
+      </c>
+      <c r="B4397" s="17">
+        <v>474449</v>
+      </c>
+    </row>
+    <row r="4398" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4398" t="s">
+        <v>4028</v>
+      </c>
+      <c r="B4398" s="17">
+        <v>485734</v>
+      </c>
+    </row>
+    <row r="4399" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4399" t="s">
+        <v>4029</v>
+      </c>
+      <c r="B4399" s="17">
+        <v>501868</v>
+      </c>
+    </row>
+    <row r="4400" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4400" t="s">
+        <v>4030</v>
+      </c>
+      <c r="B4400" s="17">
+        <v>545233</v>
+      </c>
+    </row>
+    <row r="4401" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4401" t="s">
+        <v>4031</v>
+      </c>
+      <c r="B4401" s="17">
+        <v>403469</v>
+      </c>
+    </row>
+    <row r="4402" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4402" t="s">
+        <v>4032</v>
+      </c>
+      <c r="B4402" s="17">
+        <v>288599</v>
+      </c>
+    </row>
+    <row r="4403" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4403" t="s">
+        <v>4033</v>
+      </c>
+      <c r="B4403" s="17">
+        <v>469825</v>
+      </c>
+    </row>
+    <row r="4404" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4404" t="s">
+        <v>4034</v>
+      </c>
+      <c r="B4404" s="17">
+        <v>492440</v>
+      </c>
+    </row>
+    <row r="4405" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4405" t="s">
+        <v>4035</v>
+      </c>
+      <c r="B4405" s="17">
+        <v>515627</v>
+      </c>
+    </row>
+    <row r="4406" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4406" t="s">
+        <v>4036</v>
+      </c>
+      <c r="B4406" s="17">
+        <v>525967</v>
+      </c>
+    </row>
+    <row r="4407" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4407" t="s">
+        <v>4037</v>
+      </c>
+      <c r="B4407" s="17">
+        <v>564123</v>
+      </c>
+    </row>
+    <row r="4408" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4408" t="s">
+        <v>4038</v>
+      </c>
+      <c r="B4408" s="17">
+        <v>379546</v>
+      </c>
+    </row>
+    <row r="4409" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4409" t="s">
+        <v>4039</v>
+      </c>
+      <c r="B4409" s="17">
+        <v>265742</v>
+      </c>
+    </row>
+    <row r="4410" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4410" t="s">
+        <v>4040</v>
+      </c>
+      <c r="B4410" s="17">
+        <v>488986</v>
+      </c>
+    </row>
+    <row r="4411" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4411" t="s">
+        <v>4041</v>
+      </c>
+      <c r="B4411" s="17">
+        <v>505227</v>
+      </c>
+    </row>
+    <row r="4412" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4412" t="s">
+        <v>4042</v>
+      </c>
+      <c r="B4412" s="17">
+        <v>513739</v>
+      </c>
+    </row>
+    <row r="4413" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4413" t="s">
+        <v>4043</v>
+      </c>
+      <c r="B4413" s="17">
+        <v>532124</v>
+      </c>
+    </row>
+    <row r="4414" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4414" t="s">
+        <v>4044</v>
+      </c>
+      <c r="B4414" s="17">
+        <v>592179</v>
+      </c>
+    </row>
+    <row r="4415" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4415" t="s">
+        <v>4045</v>
+      </c>
+      <c r="B4415" s="17">
+        <v>413190</v>
+      </c>
+    </row>
+    <row r="4416" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4416" t="s">
+        <v>255</v>
+      </c>
+      <c r="B4416" s="17">
+        <v>13616389</v>
+      </c>
+    </row>
+    <row r="4417" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4417" s="18">
+        <v>45300</v>
+      </c>
+      <c r="B4417" s="17">
+        <v>292419</v>
+      </c>
+    </row>
+    <row r="4418" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4418" s="18">
+        <v>45331</v>
+      </c>
+      <c r="B4418" s="17">
+        <v>490342</v>
+      </c>
+    </row>
+    <row r="4419" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4419" s="18">
+        <v>45360</v>
+      </c>
+      <c r="B4419" s="17">
+        <v>507980</v>
+      </c>
+    </row>
+    <row r="4420" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4420" s="18">
+        <v>45391</v>
+      </c>
+      <c r="B4420" s="17">
+        <v>506650</v>
+      </c>
+    </row>
+    <row r="4421" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4421" s="18">
+        <v>45421</v>
+      </c>
+      <c r="B4421" s="17">
+        <v>536612</v>
+      </c>
+    </row>
+    <row r="4422" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4422" s="18">
+        <v>45452</v>
+      </c>
+      <c r="B4422" s="17">
+        <v>555635</v>
+      </c>
+    </row>
+    <row r="4423" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4423" s="18">
+        <v>45482</v>
+      </c>
+      <c r="B4423" s="17">
+        <v>386638</v>
+      </c>
+    </row>
+    <row r="4424" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4424" s="18">
+        <v>45513</v>
+      </c>
+      <c r="B4424" s="17">
+        <v>286221</v>
+      </c>
+    </row>
+    <row r="4425" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4425" s="18">
+        <v>45544</v>
+      </c>
+      <c r="B4425" s="17">
+        <v>500563</v>
+      </c>
+    </row>
+    <row r="4426" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4426" s="18">
+        <v>45574</v>
+      </c>
+      <c r="B4426" s="17">
+        <v>508343</v>
+      </c>
+    </row>
+    <row r="4427" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4427" s="18">
+        <v>45605</v>
+      </c>
+      <c r="B4427" s="17">
+        <v>544085</v>
+      </c>
+    </row>
+    <row r="4428" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4428" s="18">
+        <v>45635</v>
+      </c>
+      <c r="B4428" s="17">
+        <v>520260</v>
+      </c>
+    </row>
+    <row r="4429" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4429" t="s">
+        <v>4046</v>
+      </c>
+      <c r="B4429" s="17">
+        <v>548449</v>
+      </c>
+    </row>
+    <row r="4430" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4430" t="s">
+        <v>4047</v>
+      </c>
+      <c r="B4430" s="17">
+        <v>376913</v>
+      </c>
+    </row>
+    <row r="4431" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4431" t="s">
+        <v>4048</v>
+      </c>
+      <c r="B4431" s="17">
+        <v>299705</v>
+      </c>
+    </row>
+    <row r="4432" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4432" t="s">
+        <v>4049</v>
+      </c>
+      <c r="B4432" s="17">
+        <v>467790</v>
+      </c>
+    </row>
+    <row r="4433" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4433" t="s">
+        <v>4050</v>
+      </c>
+      <c r="B4433" s="17">
+        <v>487231</v>
+      </c>
+    </row>
+    <row r="4434" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4434" t="s">
+        <v>4051</v>
+      </c>
+      <c r="B4434" s="17">
+        <v>489974</v>
+      </c>
+    </row>
+    <row r="4435" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4435" t="s">
+        <v>4052</v>
+      </c>
+      <c r="B4435" s="17">
+        <v>499289</v>
+      </c>
+    </row>
+    <row r="4436" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4436" t="s">
+        <v>4053</v>
+      </c>
+      <c r="B4436" s="17">
+        <v>534106</v>
+      </c>
+    </row>
+    <row r="4437" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4437" t="s">
+        <v>4054</v>
+      </c>
+      <c r="B4437" s="17">
+        <v>365886</v>
+      </c>
+    </row>
+    <row r="4438" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4438" t="s">
+        <v>4055</v>
+      </c>
+      <c r="B4438" s="17">
+        <v>254551</v>
+      </c>
+    </row>
+    <row r="4439" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4439" t="s">
+        <v>4056</v>
+      </c>
+      <c r="B4439" s="17">
+        <v>468543</v>
+      </c>
+    </row>
+    <row r="4440" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4440" t="s">
+        <v>4057</v>
+      </c>
+      <c r="B4440" s="17">
+        <v>508211</v>
+      </c>
+    </row>
+    <row r="4441" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4441" t="s">
+        <v>4058</v>
+      </c>
+      <c r="B4441" s="17">
+        <v>505632</v>
+      </c>
+    </row>
+    <row r="4442" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4442" t="s">
+        <v>4059</v>
+      </c>
+      <c r="B4442" s="17">
+        <v>533057</v>
+      </c>
+    </row>
+    <row r="4443" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4443" t="s">
+        <v>4060</v>
+      </c>
+      <c r="B4443" s="17">
+        <v>556928</v>
+      </c>
+    </row>
+    <row r="4444" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4444" t="s">
+        <v>4061</v>
+      </c>
+      <c r="B4444" s="17">
+        <v>355114</v>
+      </c>
+    </row>
+    <row r="4445" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4445" t="s">
+        <v>4062</v>
+      </c>
+      <c r="B4445" s="17">
+        <v>255728</v>
+      </c>
+    </row>
+    <row r="4446" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4446" t="s">
+        <v>4063</v>
+      </c>
+      <c r="B4446" s="17">
+        <v>473534</v>
+      </c>
+    </row>
+    <row r="4447" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4447" t="s">
+        <v>286</v>
+      </c>
+      <c r="B4447" s="17">
+        <v>13162446</v>
+      </c>
+    </row>
+    <row r="4448" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4448" s="18">
+        <v>45301</v>
+      </c>
+      <c r="B4448" s="17">
+        <v>497834</v>
+      </c>
+    </row>
+    <row r="4449" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4449" s="18">
+        <v>45332</v>
+      </c>
+      <c r="B4449" s="17">
+        <v>498701</v>
+      </c>
+    </row>
+    <row r="4450" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4450" s="18">
+        <v>45361</v>
+      </c>
+      <c r="B4450" s="17">
+        <v>512880</v>
+      </c>
+    </row>
+    <row r="4451" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4451" s="18">
+        <v>45392</v>
+      </c>
+      <c r="B4451" s="17">
+        <v>536290</v>
+      </c>
+    </row>
+    <row r="4452" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4452" s="18">
+        <v>45422</v>
+      </c>
+      <c r="B4452" s="17">
+        <v>369285</v>
+      </c>
+    </row>
+    <row r="4453" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4453" s="18">
+        <v>45453</v>
+      </c>
+      <c r="B4453" s="17">
+        <v>262407</v>
+      </c>
+    </row>
+    <row r="4454" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4454" s="18">
+        <v>45483</v>
+      </c>
+      <c r="B4454" s="17">
+        <v>472658</v>
+      </c>
+    </row>
+    <row r="4455" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4455" s="18">
+        <v>45514</v>
+      </c>
+      <c r="B4455" s="17">
+        <v>502441</v>
+      </c>
+    </row>
+    <row r="4456" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4456" s="18">
+        <v>45545</v>
+      </c>
+      <c r="B4456" s="17">
+        <v>495957</v>
+      </c>
+    </row>
+    <row r="4457" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4457" s="18">
+        <v>45575</v>
+      </c>
+      <c r="B4457" s="17">
+        <v>530580</v>
+      </c>
+    </row>
+    <row r="4458" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4458" s="18">
+        <v>45606</v>
+      </c>
+      <c r="B4458" s="17">
+        <v>506684</v>
+      </c>
+    </row>
+    <row r="4459" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4459" s="18">
+        <v>45636</v>
+      </c>
+      <c r="B4459" s="17">
+        <v>336929</v>
+      </c>
+    </row>
+    <row r="4460" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4460" t="s">
+        <v>4064</v>
+      </c>
+      <c r="B4460" s="17">
+        <v>233793</v>
+      </c>
+    </row>
+    <row r="4461" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4461" t="s">
+        <v>4065</v>
+      </c>
+      <c r="B4461" s="17">
+        <v>349919</v>
+      </c>
+    </row>
+    <row r="4462" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4462" t="s">
+        <v>4066</v>
+      </c>
+      <c r="B4462" s="17">
+        <v>374565</v>
+      </c>
+    </row>
+    <row r="4463" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4463" t="s">
+        <v>4067</v>
+      </c>
+      <c r="B4463" s="17">
+        <v>368632</v>
+      </c>
+    </row>
+    <row r="4464" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4464" t="s">
+        <v>4068</v>
+      </c>
+      <c r="B4464" s="17">
+        <v>376907</v>
+      </c>
+    </row>
+    <row r="4465" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4465" t="s">
+        <v>4069</v>
+      </c>
+      <c r="B4465" s="17">
+        <v>399195</v>
+      </c>
+    </row>
+    <row r="4466" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4466" t="s">
+        <v>4070</v>
+      </c>
+      <c r="B4466" s="17">
+        <v>331240</v>
+      </c>
+    </row>
+    <row r="4467" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4467" t="s">
+        <v>4071</v>
+      </c>
+      <c r="B4467" s="17">
+        <v>235811</v>
+      </c>
+    </row>
+    <row r="4468" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4468" t="s">
+        <v>4072</v>
+      </c>
+      <c r="B4468" s="17">
+        <v>445977</v>
+      </c>
+    </row>
+    <row r="4469" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4469" t="s">
+        <v>4073</v>
+      </c>
+      <c r="B4469" s="17">
+        <v>495392</v>
+      </c>
+    </row>
+    <row r="4470" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4470" t="s">
+        <v>4074</v>
+      </c>
+      <c r="B4470" s="17">
+        <v>486297</v>
+      </c>
+    </row>
+    <row r="4471" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4471" t="s">
+        <v>4075</v>
+      </c>
+      <c r="B4471" s="17">
+        <v>492334</v>
+      </c>
+    </row>
+    <row r="4472" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4472" t="s">
+        <v>4076</v>
+      </c>
+      <c r="B4472" s="17">
+        <v>523360</v>
+      </c>
+    </row>
+    <row r="4473" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4473" t="s">
+        <v>4077</v>
+      </c>
+      <c r="B4473" s="17">
+        <v>353851</v>
+      </c>
+    </row>
+    <row r="4474" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4474" t="s">
+        <v>4078</v>
+      </c>
+      <c r="B4474" s="17">
+        <v>241129</v>
+      </c>
+    </row>
+    <row r="4475" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4475" t="s">
+        <v>4079</v>
+      </c>
+      <c r="B4475" s="17">
+        <v>456350</v>
+      </c>
+    </row>
+    <row r="4476" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4476" t="s">
+        <v>4080</v>
+      </c>
+      <c r="B4476" s="17">
+        <v>478751</v>
+      </c>
+    </row>
+    <row r="4477" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4477" t="s">
+        <v>4081</v>
+      </c>
+      <c r="B4477" s="17">
+        <v>486684</v>
+      </c>
+    </row>
+    <row r="4478" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4478" t="s">
+        <v>4082</v>
+      </c>
+      <c r="B4478" s="17">
+        <v>509613</v>
+      </c>
+    </row>
+    <row r="4479" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4479" t="s">
+        <v>318</v>
+      </c>
+      <c r="B4479" s="17">
+        <v>13204733</v>
+      </c>
+    </row>
+    <row r="4480" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4480" s="18">
+        <v>45302</v>
+      </c>
+      <c r="B4480" s="17">
+        <v>578111</v>
+      </c>
+    </row>
+    <row r="4481" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4481" s="18">
+        <v>45333</v>
+      </c>
+      <c r="B4481" s="17">
+        <v>378041</v>
+      </c>
+    </row>
+    <row r="4482" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4482" s="18">
+        <v>45362</v>
+      </c>
+      <c r="B4482" s="17">
+        <v>251158</v>
+      </c>
+    </row>
+    <row r="4483" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4483" s="18">
+        <v>45393</v>
+      </c>
+      <c r="B4483" s="17">
+        <v>459262</v>
+      </c>
+    </row>
+    <row r="4484" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4484" s="18">
+        <v>45423</v>
+      </c>
+      <c r="B4484" s="17">
+        <v>473339</v>
+      </c>
+    </row>
+    <row r="4485" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4485" s="18">
+        <v>45454</v>
+      </c>
+      <c r="B4485" s="17">
+        <v>475156</v>
+      </c>
+    </row>
+    <row r="4486" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4486" s="18">
+        <v>45484</v>
+      </c>
+      <c r="B4486" s="17">
+        <v>492911</v>
+      </c>
+    </row>
+    <row r="4487" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4487" s="18">
+        <v>45515</v>
+      </c>
+      <c r="B4487" s="17">
+        <v>510847</v>
+      </c>
+    </row>
+    <row r="4488" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4488" s="18">
+        <v>45546</v>
+      </c>
+      <c r="B4488" s="17">
+        <v>342688</v>
+      </c>
+    </row>
+    <row r="4489" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4489" s="18">
+        <v>45576</v>
+      </c>
+      <c r="B4489" s="17">
+        <v>237923</v>
+      </c>
+    </row>
+    <row r="4490" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4490" s="18">
+        <v>45607</v>
+      </c>
+      <c r="B4490" s="17">
+        <v>450382</v>
+      </c>
+    </row>
+    <row r="4491" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4491" s="18">
+        <v>45637</v>
+      </c>
+      <c r="B4491" s="17">
+        <v>473436</v>
+      </c>
+    </row>
+    <row r="4492" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4492" t="s">
+        <v>4083</v>
+      </c>
+      <c r="B4492" s="17">
+        <v>473001</v>
+      </c>
+    </row>
+    <row r="4493" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4493" t="s">
+        <v>4084</v>
+      </c>
+      <c r="B4493" s="17">
+        <v>487634</v>
+      </c>
+    </row>
+    <row r="4494" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4494" t="s">
+        <v>4085</v>
+      </c>
+      <c r="B4494" s="17">
+        <v>547611</v>
+      </c>
+    </row>
+    <row r="4495" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4495" t="s">
+        <v>4086</v>
+      </c>
+      <c r="B4495" s="17">
+        <v>345773</v>
+      </c>
+    </row>
+    <row r="4496" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4496" t="s">
+        <v>4087</v>
+      </c>
+      <c r="B4496" s="17">
+        <v>244557</v>
+      </c>
+    </row>
+    <row r="4497" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4497" t="s">
+        <v>4088</v>
+      </c>
+      <c r="B4497" s="17">
+        <v>451930</v>
+      </c>
+    </row>
+    <row r="4498" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4498" t="s">
+        <v>4089</v>
+      </c>
+      <c r="B4498" s="17">
+        <v>484900</v>
+      </c>
+    </row>
+    <row r="4499" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4499" t="s">
+        <v>4090</v>
+      </c>
+      <c r="B4499" s="17">
+        <v>489092</v>
+      </c>
+    </row>
+    <row r="4500" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4500" t="s">
+        <v>4091</v>
+      </c>
+      <c r="B4500" s="17">
+        <v>524504</v>
+      </c>
+    </row>
+    <row r="4501" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4501" t="s">
+        <v>4092</v>
+      </c>
+      <c r="B4501" s="17">
+        <v>558020</v>
+      </c>
+    </row>
+    <row r="4502" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4502" t="s">
+        <v>4093</v>
+      </c>
+      <c r="B4502" s="17">
+        <v>364013</v>
+      </c>
+    </row>
+    <row r="4503" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4503" t="s">
+        <v>4094</v>
+      </c>
+      <c r="B4503" s="17">
+        <v>235045</v>
+      </c>
+    </row>
+    <row r="4504" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4504" t="s">
+        <v>4095</v>
+      </c>
+      <c r="B4504" s="17">
+        <v>450565</v>
+      </c>
+    </row>
+    <row r="4505" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4505" t="s">
+        <v>4096</v>
+      </c>
+      <c r="B4505" s="17">
+        <v>474186</v>
+      </c>
+    </row>
+    <row r="4506" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4506" t="s">
+        <v>4097</v>
+      </c>
+      <c r="B4506" s="17">
+        <v>479813</v>
+      </c>
+    </row>
+    <row r="4507" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4507" t="s">
+        <v>4098</v>
+      </c>
+      <c r="B4507" s="17">
+        <v>511832</v>
+      </c>
+    </row>
+    <row r="4508" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4508" t="s">
+        <v>4099</v>
+      </c>
+      <c r="B4508" s="17">
+        <v>582263</v>
+      </c>
+    </row>
+    <row r="4509" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4509" t="s">
+        <v>4100</v>
+      </c>
+      <c r="B4509" s="17">
+        <v>376740</v>
+      </c>
+    </row>
+    <row r="4510" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4510" t="s">
+        <v>349</v>
+      </c>
+      <c r="B4510" s="17">
+        <v>11401405</v>
+      </c>
+    </row>
+    <row r="4511" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4511" s="18">
+        <v>45303</v>
+      </c>
+      <c r="B4511" s="17">
+        <v>264752</v>
+      </c>
+    </row>
+    <row r="4512" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4512" s="18">
+        <v>45334</v>
+      </c>
+      <c r="B4512" s="17">
+        <v>469763</v>
+      </c>
+    </row>
+    <row r="4513" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4513" s="18">
+        <v>45363</v>
+      </c>
+      <c r="B4513" s="17">
+        <v>488789</v>
+      </c>
+    </row>
+    <row r="4514" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4514" s="18">
+        <v>45394</v>
+      </c>
+      <c r="B4514" s="17">
+        <v>495476</v>
+      </c>
+    </row>
+    <row r="4515" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4515" s="18">
+        <v>45424</v>
+      </c>
+      <c r="B4515" s="17">
+        <v>507515</v>
+      </c>
+    </row>
+    <row r="4516" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4516" s="18">
+        <v>45455</v>
+      </c>
+      <c r="B4516" s="17">
+        <v>562757</v>
+      </c>
+    </row>
+    <row r="4517" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4517" s="18">
+        <v>45485</v>
+      </c>
+      <c r="B4517" s="17">
+        <v>375991</v>
+      </c>
+    </row>
+    <row r="4518" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4518" s="18">
+        <v>45516</v>
+      </c>
+      <c r="B4518" s="17">
+        <v>260518</v>
+      </c>
+    </row>
+    <row r="4519" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4519" s="18">
+        <v>45547</v>
+      </c>
+      <c r="B4519" s="17">
+        <v>466274</v>
+      </c>
+    </row>
+    <row r="4520" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4520" s="18">
+        <v>45577</v>
+      </c>
+      <c r="B4520" s="17">
+        <v>487932</v>
+      </c>
+    </row>
+    <row r="4521" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4521" s="18">
+        <v>45608</v>
+      </c>
+      <c r="B4521" s="17">
+        <v>487816</v>
+      </c>
+    </row>
+    <row r="4522" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4522" s="18">
+        <v>45638</v>
+      </c>
+      <c r="B4522" s="17">
+        <v>510489</v>
+      </c>
+    </row>
+    <row r="4523" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4523" t="s">
+        <v>4101</v>
+      </c>
+      <c r="B4523" s="17">
+        <v>556043</v>
+      </c>
+    </row>
+    <row r="4524" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4524" t="s">
+        <v>4102</v>
+      </c>
+      <c r="B4524" s="17">
+        <v>363516</v>
+      </c>
+    </row>
+    <row r="4525" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4525" t="s">
+        <v>4103</v>
+      </c>
+      <c r="B4525" s="17">
+        <v>257398</v>
+      </c>
+    </row>
+    <row r="4526" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4526" t="s">
+        <v>4104</v>
+      </c>
+      <c r="B4526" s="17">
+        <v>470192</v>
+      </c>
+    </row>
+    <row r="4527" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4527" t="s">
+        <v>4105</v>
+      </c>
+      <c r="B4527" s="17">
+        <v>484637</v>
+      </c>
+    </row>
+    <row r="4528" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4528" t="s">
+        <v>4106</v>
+      </c>
+      <c r="B4528" s="17">
+        <v>487921</v>
+      </c>
+    </row>
+    <row r="4529" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4529" t="s">
+        <v>4107</v>
+      </c>
+      <c r="B4529" s="17">
+        <v>506930</v>
+      </c>
+    </row>
+    <row r="4530" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4530" t="s">
+        <v>4108</v>
+      </c>
+      <c r="B4530" s="17">
+        <v>492775</v>
+      </c>
+    </row>
+    <row r="4531" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4531" t="s">
+        <v>4109</v>
+      </c>
+      <c r="B4531" s="17">
+        <v>311296</v>
+      </c>
+    </row>
+    <row r="4532" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4532" t="s">
+        <v>4110</v>
+      </c>
+      <c r="B4532" s="17">
+        <v>243654</v>
+      </c>
+    </row>
+    <row r="4533" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4533" t="s">
+        <v>4111</v>
+      </c>
+      <c r="B4533" s="17">
+        <v>250705</v>
+      </c>
+    </row>
+    <row r="4534" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4534" t="s">
+        <v>4112</v>
+      </c>
+      <c r="B4534" s="17">
+        <v>116267</v>
+      </c>
+    </row>
+    <row r="4535" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4535" t="s">
+        <v>4113</v>
+      </c>
+      <c r="B4535" s="17">
+        <v>116859</v>
+      </c>
+    </row>
+    <row r="4536" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4536" t="s">
+        <v>4114</v>
+      </c>
+      <c r="B4536" s="17">
+        <v>158357</v>
+      </c>
+    </row>
+    <row r="4537" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4537" t="s">
+        <v>4115</v>
+      </c>
+      <c r="B4537" s="17">
+        <v>274163</v>
+      </c>
+    </row>
+    <row r="4538" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4538" t="s">
+        <v>4116</v>
+      </c>
+      <c r="B4538" s="17">
+        <v>247369</v>
+      </c>
+    </row>
+    <row r="4539" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4539" t="s">
+        <v>4117</v>
+      </c>
+      <c r="B4539" s="17">
+        <v>205694</v>
+      </c>
+    </row>
+    <row r="4540" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4540" t="s">
+        <v>4118</v>
+      </c>
+      <c r="B4540" s="17">
+        <v>277457</v>
+      </c>
+    </row>
+    <row r="4541" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4541" t="s">
+        <v>4119</v>
+      </c>
+      <c r="B4541" s="17">
+        <v>202100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
